--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C495C53-540F-8F4A-8581-D45B33C883F5}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC1F9225-FAF9-4536-BAB1-20D3A4E9E05D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gràfics!$A$1:$B$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$N$1:$O$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="248">
   <si>
     <t>Participants</t>
   </si>
@@ -904,7 +905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -926,7 +927,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6008,24 +6008,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.953125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.953125" customWidth="1"/>
-    <col min="5" max="6" width="16.0078125" customWidth="1"/>
-    <col min="7" max="7" width="14.9296875" customWidth="1"/>
-    <col min="8" max="8" width="13.98828125" customWidth="1"/>
-    <col min="9" max="9" width="18.96484375" customWidth="1"/>
-    <col min="10" max="10" width="14.9296875" customWidth="1"/>
-    <col min="11" max="11" width="11.97265625" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.953125" customWidth="1"/>
-    <col min="14" max="14" width="18.96484375" customWidth="1"/>
-    <col min="15" max="15" width="9.953125" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6101,13 +6101,13 @@
         <v>229</v>
       </c>
       <c r="N2" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="O2" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>110</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>229</v>
@@ -6162,13 +6162,13 @@
         <v>229</v>
       </c>
       <c r="N4" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="O4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>87</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>229</v>
@@ -6191,13 +6191,13 @@
         <v>229</v>
       </c>
       <c r="N5" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="O5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6217,13 +6217,13 @@
         <v>229</v>
       </c>
       <c r="N6" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="O6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6243,13 +6243,13 @@
         <v>229</v>
       </c>
       <c r="N7" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="O7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6269,13 +6269,13 @@
         <v>229</v>
       </c>
       <c r="N8" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6295,13 +6295,13 @@
         <v>229</v>
       </c>
       <c r="N9" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="O9" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6318,13 +6318,13 @@
         <v>229</v>
       </c>
       <c r="N10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6341,13 +6341,13 @@
         <v>229</v>
       </c>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="O11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6358,19 +6358,19 @@
         <v>127</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6380,21 +6380,20 @@
       <c r="C13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="14" t="str">
-        <f>+C18</f>
-        <v>Japó</v>
+      <c r="E13" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N13" t="s">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6404,21 +6403,20 @@
       <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="14" t="str">
-        <f>+C20</f>
-        <v>Nova Zelanda</v>
+      <c r="E14" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N14" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="O14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6428,15 +6426,14 @@
       <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="14" t="str">
-        <f>+C21</f>
-        <v>Iran</v>
+      <c r="E15" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6446,15 +6443,14 @@
       <c r="C16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="14" t="str">
-        <f>+C23</f>
-        <v>Uruguai</v>
+      <c r="E16" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6462,17 +6458,16 @@
         <v>228</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="14" t="str">
-        <f>+C24</f>
-        <v>Aràbia Saudita</v>
+        <v>91</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6482,12 +6477,11 @@
       <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="14" t="str">
-        <f>+C26</f>
-        <v>Noruega</v>
+      <c r="E18" s="14" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6495,14 +6489,13 @@
         <v>231</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="14" t="str">
-        <f>+C27</f>
-        <v>França</v>
+        <v>103</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6510,14 +6503,13 @@
         <v>228</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="14" t="str">
-        <f>+C29</f>
-        <v>Argentina</v>
+        <v>104</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6527,12 +6519,11 @@
       <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="14" t="str">
-        <f>+C30</f>
-        <v>Àustria</v>
+      <c r="E21" s="14" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6542,12 +6533,11 @@
       <c r="C22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="14" t="str">
-        <f>+C32</f>
-        <v>Colòmbia</v>
+      <c r="E22" s="14" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6555,14 +6545,13 @@
         <v>228</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="14" t="str">
-        <f>+C33</f>
-        <v>RD Congo</v>
+        <v>93</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6570,14 +6559,13 @@
         <v>230</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="14" t="str">
-        <f>+C35</f>
-        <v>Anglaterra</v>
+        <v>105</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6585,14 +6573,13 @@
         <v>231</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="14" t="str">
-        <f>+C36</f>
-        <v>Ghana</v>
+        <v>143</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6603,11 +6590,11 @@
         <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6621,7 +6608,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6632,10 +6619,10 @@
         <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6649,7 +6636,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6660,10 +6647,10 @@
         <v>107</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6677,7 +6664,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6691,7 +6678,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6705,7 +6692,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6716,7 +6703,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6727,7 +6714,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6738,7 +6725,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6750,6 +6737,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="N1:O14" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:O14">
+      <sortCondition descending="1" ref="O1:O14"/>
+    </sortState>
+  </autoFilter>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{E4A41900-CC37-48F7-B004-B74485AD8A27}">
       <formula1>$C$2:$C$37</formula1>
@@ -6789,81 +6781,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.45703125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7117,7 +7109,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7333,15 +7325,15 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7369,7 +7361,7 @@
       </c>
       <c r="CD2">
         <f>IFERROR(VLOOKUP(BT2,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE2">
         <f>IF(BR2='Resultats Reals'!$L$2,5,0)</f>
@@ -7377,10 +7369,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>43.5</v>
+        <v>48.5</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7596,15 +7588,15 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7640,10 +7632,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7859,15 +7851,15 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7903,10 +7895,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8122,11 +8114,11 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
@@ -8166,10 +8158,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8385,11 +8377,11 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
@@ -8429,10 +8421,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8648,15 +8640,15 @@
       </c>
       <c r="BU7">
         <f>IF(C7='Resultats Reals'!$C$2,2,IF(OR(C7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C7)&gt;0),1,0))+IF(D7='Resultats Reals'!$C$5,2,IF(OR(D7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D7)&gt;0),1,0))+IF(E7='Resultats Reals'!$C$8,2,IF(OR(E7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E7)&gt;0),1,0))+IF(F7='Resultats Reals'!$C$11,2,IF(OR(F7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F7)&gt;0),1,0))+IF(G7='Resultats Reals'!$C$14,2,IF(OR(G7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G7)&gt;0),1,0))+IF(H7='Resultats Reals'!$C$17,2,IF(OR(H7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H7)&gt;0),1,0))+IF(I7='Resultats Reals'!$C$20,2,IF(OR(I7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I7)&gt;0),1,0))+IF(J7='Resultats Reals'!$C$23,2,IF(OR(J7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J7)&gt;0),1,0))+IF(K7='Resultats Reals'!$C$26,2,IF(OR(K7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K7)&gt;0),1,0))+IF(L7='Resultats Reals'!$C$29,2,IF(OR(L7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L7)&gt;0),1,0))+IF(M7='Resultats Reals'!$C$32,2,IF(OR(M7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M7)&gt;0),1,0))+IF(N7='Resultats Reals'!$C$35,2,IF(OR(N7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N7)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z7)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8692,10 +8684,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8911,7 +8903,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N8)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
@@ -8919,7 +8911,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -8955,10 +8947,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9177,11 +9169,11 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N9)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z9)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
@@ -9221,10 +9213,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>46.5</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9440,11 +9432,11 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
@@ -9484,10 +9476,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>48.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9703,15 +9695,15 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
@@ -9747,10 +9739,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>46.5</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -9966,15 +9958,15 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N12)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
@@ -10010,10 +10002,10 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -10229,15 +10221,15 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10273,10 +10265,10 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -10492,11 +10484,11 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
@@ -10536,10 +10528,10 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>157</v>
       </c>
@@ -10755,15 +10747,15 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
@@ -10799,10 +10791,10 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>47.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -11018,15 +11010,15 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11062,10 +11054,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -11285,7 +11277,7 @@
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
@@ -11325,10 +11317,10 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -11547,11 +11539,11 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
@@ -11591,10 +11583,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -11810,7 +11802,7 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
@@ -11854,10 +11846,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -12073,11 +12065,11 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
@@ -12117,10 +12109,10 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -12336,11 +12328,11 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
@@ -12380,10 +12372,10 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>46.5</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -12599,15 +12591,15 @@
       </c>
       <c r="BU22">
         <f>IF(C22='Resultats Reals'!$C$2,2,IF(OR(C22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C22)&gt;0),1,0))+IF(D22='Resultats Reals'!$C$5,2,IF(OR(D22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D22)&gt;0),1,0))+IF(E22='Resultats Reals'!$C$8,2,IF(OR(E22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E22)&gt;0),1,0))+IF(F22='Resultats Reals'!$C$11,2,IF(OR(F22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F22)&gt;0),1,0))+IF(G22='Resultats Reals'!$C$14,2,IF(OR(G22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G22)&gt;0),1,0))+IF(H22='Resultats Reals'!$C$17,2,IF(OR(H22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H22)&gt;0),1,0))+IF(I22='Resultats Reals'!$C$20,2,IF(OR(I22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I22)&gt;0),1,0))+IF(J22='Resultats Reals'!$C$23,2,IF(OR(J22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J22)&gt;0),1,0))+IF(K22='Resultats Reals'!$C$26,2,IF(OR(K22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K22)&gt;0),1,0))+IF(L22='Resultats Reals'!$C$29,2,IF(OR(L22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L22)&gt;0),1,0))+IF(M22='Resultats Reals'!$C$32,2,IF(OR(M22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M22)&gt;0),1,0))+IF(N22='Resultats Reals'!$C$35,2,IF(OR(N22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N22)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX22">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB22)&gt;0,1,0)</f>
@@ -12643,10 +12635,10 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -12862,15 +12854,15 @@
       </c>
       <c r="BU23">
         <f>IF(C23='Resultats Reals'!$C$2,2,IF(OR(C23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C23)&gt;0),1,0))+IF(D23='Resultats Reals'!$C$5,2,IF(OR(D23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D23)&gt;0),1,0))+IF(E23='Resultats Reals'!$C$8,2,IF(OR(E23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E23)&gt;0),1,0))+IF(F23='Resultats Reals'!$C$11,2,IF(OR(F23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F23)&gt;0),1,0))+IF(G23='Resultats Reals'!$C$14,2,IF(OR(G23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G23)&gt;0),1,0))+IF(H23='Resultats Reals'!$C$17,2,IF(OR(H23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H23)&gt;0),1,0))+IF(I23='Resultats Reals'!$C$20,2,IF(OR(I23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I23)&gt;0),1,0))+IF(J23='Resultats Reals'!$C$23,2,IF(OR(J23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J23)&gt;0),1,0))+IF(K23='Resultats Reals'!$C$26,2,IF(OR(K23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K23)&gt;0),1,0))+IF(L23='Resultats Reals'!$C$29,2,IF(OR(L23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L23)&gt;0),1,0))+IF(M23='Resultats Reals'!$C$32,2,IF(OR(M23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M23)&gt;0),1,0))+IF(N23='Resultats Reals'!$C$35,2,IF(OR(N23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N23)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX23">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB23)&gt;0,1,0)</f>
@@ -12906,10 +12898,10 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -13125,15 +13117,15 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13169,10 +13161,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>175</v>
       </c>
@@ -13388,15 +13380,15 @@
       </c>
       <c r="BU25">
         <f>IF(C25='Resultats Reals'!$C$2,2,IF(OR(C25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C25)&gt;0),1,0))+IF(D25='Resultats Reals'!$C$5,2,IF(OR(D25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D25)&gt;0),1,0))+IF(E25='Resultats Reals'!$C$8,2,IF(OR(E25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E25)&gt;0),1,0))+IF(F25='Resultats Reals'!$C$11,2,IF(OR(F25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F25)&gt;0),1,0))+IF(G25='Resultats Reals'!$C$14,2,IF(OR(G25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G25)&gt;0),1,0))+IF(H25='Resultats Reals'!$C$17,2,IF(OR(H25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H25)&gt;0),1,0))+IF(I25='Resultats Reals'!$C$20,2,IF(OR(I25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I25)&gt;0),1,0))+IF(J25='Resultats Reals'!$C$23,2,IF(OR(J25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J25)&gt;0),1,0))+IF(K25='Resultats Reals'!$C$26,2,IF(OR(K25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K25)&gt;0),1,0))+IF(L25='Resultats Reals'!$C$29,2,IF(OR(L25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L25)&gt;0),1,0))+IF(M25='Resultats Reals'!$C$32,2,IF(OR(M25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M25)&gt;0),1,0))+IF(N25='Resultats Reals'!$C$35,2,IF(OR(N25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N25)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX25">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB25)&gt;0,1,0)</f>
@@ -13432,10 +13424,10 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -13654,11 +13646,11 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
@@ -13698,10 +13690,10 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -13917,11 +13909,11 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
@@ -13953,7 +13945,7 @@
       </c>
       <c r="CD27">
         <f>IFERROR(VLOOKUP(BT27,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE27">
         <f>IF(BR27='Resultats Reals'!$L$2,5,0)</f>
@@ -13961,10 +13953,10 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>179</v>
       </c>
@@ -14180,15 +14172,15 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N28)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z28)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14224,10 +14216,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>181</v>
       </c>
@@ -14446,15 +14438,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14490,10 +14482,10 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14709,15 +14701,15 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14745,7 +14737,7 @@
       </c>
       <c r="CD30">
         <f>IFERROR(VLOOKUP(BT30,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE30">
         <f>IF(BR30='Resultats Reals'!$L$2,5,0)</f>
@@ -14753,10 +14745,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -14972,11 +14964,11 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
@@ -15016,10 +15008,10 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -15238,15 +15230,15 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15282,10 +15274,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -15504,11 +15496,11 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
@@ -15540,7 +15532,7 @@
       </c>
       <c r="CD33">
         <f>IFERROR(VLOOKUP(BT33,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE33">
         <f>IF(BR33='Resultats Reals'!$L$2,5,0)</f>
@@ -15548,10 +15540,10 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -15770,15 +15762,15 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15814,10 +15806,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -16033,11 +16025,11 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
@@ -16077,10 +16069,10 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -16296,11 +16288,11 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N36)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z36)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
@@ -16340,10 +16332,10 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -16559,15 +16551,15 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16603,10 +16595,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -16825,15 +16817,15 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16869,10 +16861,10 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -17091,15 +17083,15 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N39)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
@@ -17135,10 +17127,10 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -17357,15 +17349,15 @@
       </c>
       <c r="BU40">
         <f>IF(C40='Resultats Reals'!$C$2,2,IF(OR(C40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C40)&gt;0),1,0))+IF(D40='Resultats Reals'!$C$5,2,IF(OR(D40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D40)&gt;0),1,0))+IF(E40='Resultats Reals'!$C$8,2,IF(OR(E40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E40)&gt;0),1,0))+IF(F40='Resultats Reals'!$C$11,2,IF(OR(F40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F40)&gt;0),1,0))+IF(G40='Resultats Reals'!$C$14,2,IF(OR(G40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G40)&gt;0),1,0))+IF(H40='Resultats Reals'!$C$17,2,IF(OR(H40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H40)&gt;0),1,0))+IF(I40='Resultats Reals'!$C$20,2,IF(OR(I40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I40)&gt;0),1,0))+IF(J40='Resultats Reals'!$C$23,2,IF(OR(J40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J40)&gt;0),1,0))+IF(K40='Resultats Reals'!$C$26,2,IF(OR(K40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K40)&gt;0),1,0))+IF(L40='Resultats Reals'!$C$29,2,IF(OR(L40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L40)&gt;0),1,0))+IF(M40='Resultats Reals'!$C$32,2,IF(OR(M40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M40)&gt;0),1,0))+IF(N40='Resultats Reals'!$C$35,2,IF(OR(N40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N40)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z40)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17401,10 +17393,10 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -17620,11 +17612,11 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N41)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
@@ -17664,10 +17656,10 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -17883,15 +17875,15 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N42)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z42)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17927,10 +17919,10 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -18149,11 +18141,11 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N43)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z43)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
@@ -18193,10 +18185,10 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -18412,15 +18404,15 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N44)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z44)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18456,10 +18448,10 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>52.5</v>
       </c>
     </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>209</v>
       </c>
@@ -18675,15 +18667,15 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N45)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z45)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18719,10 +18711,10 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -18941,15 +18933,15 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N46)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z46)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -18985,10 +18977,10 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -19204,15 +19196,15 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N47)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z47)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
@@ -19248,10 +19240,10 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -19467,15 +19459,15 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N48)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z48)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19511,10 +19503,10 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -19733,15 +19725,15 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N49)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z49)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19777,7 +19769,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -19788,13 +19780,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.2890625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>244</v>
       </c>
@@ -19802,395 +19794,395 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2">
         <v>45.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3">
         <v>45.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>44.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>44.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>42.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>42.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>42.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14">
         <v>41.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15">
         <v>41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22">
         <v>40.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23">
         <v>40.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24">
         <v>40.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26">
         <v>39.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27">
         <v>39.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28">
         <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29">
         <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30">
         <v>39.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31">
         <v>39.5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35">
         <v>38.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36">
         <v>38.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37">
         <v>38.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38">
         <v>38.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40">
         <v>37.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41">
         <v>37.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42">
         <v>36.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43">
         <v>36.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45">
         <v>34.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46">
         <v>34.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47">
         <v>34.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48">
         <v>32.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49">
         <v>28.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50">
         <v>1906</v>
       </c>
     </row>
@@ -20203,247 +20195,247 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>247</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC1F9225-FAF9-4536-BAB1-20D3A4E9E05D}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33CCDFAC-495C-4070-89CE-2F6978D2A099}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gràfics!$A$1:$B$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$N$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$R$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
@@ -42,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="248">
   <si>
     <t>Participants</t>
   </si>
@@ -774,9 +796,6 @@
     <t>Grup L</t>
   </si>
   <si>
-    <t xml:space="preserve">Panamà </t>
-  </si>
-  <si>
     <t>Participant</t>
   </si>
   <si>
@@ -786,7 +805,10 @@
     <t>Total general</t>
   </si>
   <si>
-    <t>``</t>
+    <t>Bòsnia i Hercegovina</t>
+  </si>
+  <si>
+    <t>Verificació Països</t>
   </si>
 </sst>
 </file>
@@ -821,7 +843,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -859,6 +881,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -905,7 +933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -927,6 +955,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,6 +974,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6007,25 +6043,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6035,38 +6079,53 @@
       <c r="C1" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="D1" s="15" t="s">
+        <v>247</v>
+      </c>
       <c r="E1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6076,38 +6135,58 @@
       <c r="C2" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="D2" s="2" t="str" cm="1">
+        <f t="array" ref="D2">IF(SUMPRODUCT(--EXACT(C2,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E2" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>229</v>
+        <v>90</v>
+      </c>
+      <c r="F2" s="2" t="str" cm="1">
+        <f t="array" ref="F2">IF(SUMPRODUCT(--EXACT(E2,C2:C37))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>229</v>
+      <c r="H2" s="2" t="str" cm="1">
+        <f t="array" ref="H2">IF(SUMPRODUCT(--EXACT(G2,E2:E37))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>229</v>
+      <c r="J2" s="2" t="str" cm="1">
+        <f t="array" ref="J2">IF(SUMPRODUCT(--EXACT(I2,G2:G37))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="2" t="str" cm="1">
+        <f t="array" ref="L2">IF(SUMPRODUCT(--EXACT(K2,I2:I37))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="R2" t="s">
         <v>158</v>
       </c>
-      <c r="O2" s="3">
+      <c r="S2" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6117,29 +6196,49 @@
       <c r="C3" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="D3" s="2" t="str" cm="1">
+        <f t="array" ref="D3">IF(SUMPRODUCT(--EXACT(C3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>229</v>
+        <v>97</v>
+      </c>
+      <c r="F3" s="2" t="str" cm="1">
+        <f t="array" ref="F3">IF(SUMPRODUCT(--EXACT(E3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>229</v>
+      <c r="H3" s="2" t="str" cm="1">
+        <f t="array" ref="H3">IF(SUMPRODUCT(--EXACT(G3,E3:E38))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N3" t="s">
+      <c r="J3" s="2" t="str" cm="1">
+        <f t="array" ref="J3">IF(SUMPRODUCT(--EXACT(I3,G3:G38))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L3" s="2" t="str" cm="1">
+        <f t="array" ref="L3">IF(SUMPRODUCT(--EXACT(K3,I3:I38))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="R3" t="s">
         <v>162</v>
       </c>
-      <c r="O3" s="3">
+      <c r="S3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6149,26 +6248,43 @@
       <c r="C4" s="3" t="s">
         <v>110</v>
       </c>
+      <c r="D4" s="2" t="str" cm="1">
+        <f t="array" ref="D4">IF(SUMPRODUCT(--EXACT(C4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E4" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>229</v>
+        <v>95</v>
+      </c>
+      <c r="F4" s="2" t="str" cm="1">
+        <f t="array" ref="F4">IF(SUMPRODUCT(--EXACT(E4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="2" t="str" cm="1">
+        <f t="array" ref="H4">IF(SUMPRODUCT(--EXACT(G4,E4:E39))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N4" t="s">
+      <c r="J4" s="2" t="str" cm="1">
+        <f t="array" ref="J4">IF(SUMPRODUCT(--EXACT(I4,G4:G39))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="16"/>
+      <c r="R4" t="s">
         <v>155</v>
       </c>
-      <c r="O4" s="3">
+      <c r="S4" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6176,28 +6292,45 @@
         <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
+      </c>
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">IF(SUMPRODUCT(--EXACT(C5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>229</v>
+        <v>127</v>
+      </c>
+      <c r="F5" s="2" t="str" cm="1">
+        <f t="array" ref="F5">IF(SUMPRODUCT(--EXACT(E5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="2" t="str" cm="1">
+        <f t="array" ref="H5">IF(SUMPRODUCT(--EXACT(G5,E5:E40))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N5" t="s">
+      <c r="J5" s="2" t="str" cm="1">
+        <f t="array" ref="J5">IF(SUMPRODUCT(--EXACT(I5,G5:G40))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5" s="16"/>
+      <c r="R5" t="s">
         <v>129</v>
       </c>
-      <c r="O5" s="3">
+      <c r="S5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6205,25 +6338,38 @@
         <v>230</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="D6" s="2" t="str" cm="1">
+        <f t="array" ref="D6">IF(SUMPRODUCT(--EXACT(C6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>229</v>
+        <v>107</v>
+      </c>
+      <c r="F6" s="2" t="str" cm="1">
+        <f t="array" ref="F6">IF(SUMPRODUCT(--EXACT(E6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N6" t="s">
+      <c r="H6" s="2" t="str" cm="1">
+        <f t="array" ref="H6">IF(SUMPRODUCT(--EXACT(G6,E6:E41))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="R6" t="s">
         <v>167</v>
       </c>
-      <c r="O6" s="3">
+      <c r="S6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6231,25 +6377,38 @@
         <v>231</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>246</v>
+      </c>
+      <c r="D7" s="2" t="str" cm="1">
+        <f t="array" ref="D7">IF(SUMPRODUCT(--EXACT(C7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>229</v>
+        <v>92</v>
+      </c>
+      <c r="F7" s="2" t="str" cm="1">
+        <f t="array" ref="F7">IF(SUMPRODUCT(--EXACT(E7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N7" t="s">
+      <c r="H7" s="2" t="str" cm="1">
+        <f t="array" ref="H7">IF(SUMPRODUCT(--EXACT(G7,E7:E42))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="16"/>
+      <c r="R7" t="s">
         <v>195</v>
       </c>
-      <c r="O7" s="3">
+      <c r="S7" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6259,23 +6418,36 @@
       <c r="C8" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="D8" s="2" t="str" cm="1">
+        <f t="array" ref="D8">IF(SUMPRODUCT(--EXACT(C8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E8" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>229</v>
+        <v>88</v>
+      </c>
+      <c r="F8" s="2" t="str" cm="1">
+        <f t="array" ref="F8">IF(SUMPRODUCT(--EXACT(E8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N8" t="s">
+      <c r="H8" s="2" t="str" cm="1">
+        <f t="array" ref="H8">IF(SUMPRODUCT(--EXACT(G8,E8:E43))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J8" s="16"/>
+      <c r="R8" t="s">
         <v>212</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6285,23 +6457,36 @@
       <c r="C9" s="3" t="s">
         <v>100</v>
       </c>
+      <c r="D9" s="2" t="str" cm="1">
+        <f t="array" ref="D9">IF(SUMPRODUCT(--EXACT(C9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E9" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>229</v>
+        <v>99</v>
+      </c>
+      <c r="F9" s="2" t="str" cm="1">
+        <f t="array" ref="F9">IF(SUMPRODUCT(--EXACT(E9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N9" t="s">
+      <c r="H9" s="2" t="str" cm="1">
+        <f t="array" ref="H9">IF(SUMPRODUCT(--EXACT(G9,E9:E44))&gt;0,"OK","Revisar")</f>
+        <v>Revisar</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="R9" t="s">
         <v>146</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6311,20 +6496,29 @@
       <c r="C10" s="3" t="s">
         <v>112</v>
       </c>
+      <c r="D10" s="2" t="str" cm="1">
+        <f t="array" ref="D10">IF(SUMPRODUCT(--EXACT(C10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E10" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="2" t="str" cm="1">
+        <f t="array" ref="F10">IF(SUMPRODUCT(--EXACT(E10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N10" t="s">
+      <c r="H10" s="16"/>
+      <c r="R10" t="s">
         <v>122</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6334,20 +6528,29 @@
       <c r="C11" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="D11" s="2" t="str" cm="1">
+        <f t="array" ref="D11">IF(SUMPRODUCT(--EXACT(C11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E11" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="2" t="str" cm="1">
+        <f t="array" ref="F11">IF(SUMPRODUCT(--EXACT(E11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N11" t="s">
+      <c r="H11" s="16"/>
+      <c r="R11" t="s">
         <v>123</v>
       </c>
-      <c r="O11" s="3">
+      <c r="S11" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6357,20 +6560,29 @@
       <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="D12" s="2" t="str" cm="1">
+        <f t="array" ref="D12">IF(SUMPRODUCT(--EXACT(C12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E12" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="2" t="str" cm="1">
+        <f t="array" ref="F12">IF(SUMPRODUCT(--EXACT(E12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N12" t="s">
+      <c r="H12" s="16"/>
+      <c r="R12" t="s">
         <v>134</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6380,20 +6592,29 @@
       <c r="C13" s="3" t="s">
         <v>113</v>
       </c>
+      <c r="D13" s="2" t="str" cm="1">
+        <f t="array" ref="D13">IF(SUMPRODUCT(--EXACT(C13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E13" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="2" t="str" cm="1">
+        <f t="array" ref="F13">IF(SUMPRODUCT(--EXACT(E13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N13" t="s">
+      <c r="H13" s="16"/>
+      <c r="R13" t="s">
         <v>133</v>
       </c>
-      <c r="O13" s="3">
+      <c r="S13" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6403,20 +6624,29 @@
       <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="D14" s="2" t="str" cm="1">
+        <f t="array" ref="D14">IF(SUMPRODUCT(--EXACT(C14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E14" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="2" t="str" cm="1">
+        <f t="array" ref="F14">IF(SUMPRODUCT(--EXACT(E14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N14" t="s">
+      <c r="H14" s="16"/>
+      <c r="R14" t="s">
         <v>201</v>
       </c>
-      <c r="O14" s="3">
+      <c r="S14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6426,14 +6656,23 @@
       <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="D15" s="2" t="str" cm="1">
+        <f t="array" ref="D15">IF(SUMPRODUCT(--EXACT(C15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E15" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="2" t="str" cm="1">
+        <f t="array" ref="F15">IF(SUMPRODUCT(--EXACT(E15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>229</v>
       </c>
+      <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6443,14 +6682,23 @@
       <c r="C16" s="3" t="s">
         <v>102</v>
       </c>
+      <c r="D16" s="2" t="str" cm="1">
+        <f t="array" ref="D16">IF(SUMPRODUCT(--EXACT(C16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E16" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="2" t="str" cm="1">
+        <f t="array" ref="F16">IF(SUMPRODUCT(--EXACT(E16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>229</v>
       </c>
+      <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6460,14 +6708,23 @@
       <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="D17" s="2" t="str" cm="1">
+        <f t="array" ref="D17">IF(SUMPRODUCT(--EXACT(C17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="2" t="str" cm="1">
+        <f t="array" ref="F17">IF(SUMPRODUCT(--EXACT(E17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>229</v>
       </c>
+      <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6477,11 +6734,19 @@
       <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">IF(SUMPRODUCT(--EXACT(C18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E18" s="14" t="s">
-        <v>118</v>
+        <v>89</v>
+      </c>
+      <c r="F18" s="2" t="str" cm="1">
+        <f t="array" ref="F18">IF(SUMPRODUCT(--EXACT(E18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6491,11 +6756,19 @@
       <c r="C19" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="D19" s="2" t="str" cm="1">
+        <f t="array" ref="D19">IF(SUMPRODUCT(--EXACT(C19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E19" s="14" t="s">
         <v>94</v>
       </c>
+      <c r="F19" s="2" t="str" cm="1">
+        <f t="array" ref="F19">IF(SUMPRODUCT(--EXACT(E19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6505,11 +6778,19 @@
       <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
+      <c r="D20" s="2" t="str" cm="1">
+        <f t="array" ref="D20">IF(SUMPRODUCT(--EXACT(C20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E20" s="14" t="s">
-        <v>95</v>
+        <v>121</v>
+      </c>
+      <c r="F20" s="2" t="str" cm="1">
+        <f t="array" ref="F20">IF(SUMPRODUCT(--EXACT(E20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6519,11 +6800,19 @@
       <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
+      <c r="D21" s="2" t="str" cm="1">
+        <f t="array" ref="D21">IF(SUMPRODUCT(--EXACT(C21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E21" s="14" t="s">
-        <v>107</v>
+        <v>116</v>
+      </c>
+      <c r="F21" s="2" t="str" cm="1">
+        <f t="array" ref="F21">IF(SUMPRODUCT(--EXACT(E21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6533,11 +6822,19 @@
       <c r="C22" s="3" t="s">
         <v>92</v>
       </c>
+      <c r="D22" s="2" t="str" cm="1">
+        <f t="array" ref="D22">IF(SUMPRODUCT(--EXACT(C22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E22" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
+      </c>
+      <c r="F22" s="2" t="str" cm="1">
+        <f t="array" ref="F22">IF(SUMPRODUCT(--EXACT(E22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6547,11 +6844,19 @@
       <c r="C23" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="D23" s="2" t="str" cm="1">
+        <f t="array" ref="D23">IF(SUMPRODUCT(--EXACT(C23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E23" s="14" t="s">
-        <v>128</v>
+        <v>100</v>
+      </c>
+      <c r="F23" s="2" t="str" cm="1">
+        <f t="array" ref="F23">IF(SUMPRODUCT(--EXACT(E23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6561,11 +6866,19 @@
       <c r="C24" s="3" t="s">
         <v>105</v>
       </c>
+      <c r="D24" s="2" t="str" cm="1">
+        <f t="array" ref="D24">IF(SUMPRODUCT(--EXACT(C24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E24" s="14" t="s">
-        <v>97</v>
+        <v>86</v>
+      </c>
+      <c r="F24" s="2" t="str" cm="1">
+        <f t="array" ref="F24">IF(SUMPRODUCT(--EXACT(E24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6575,11 +6888,19 @@
       <c r="C25" s="3" t="s">
         <v>143</v>
       </c>
+      <c r="D25" s="2" t="str" cm="1">
+        <f t="array" ref="D25">IF(SUMPRODUCT(--EXACT(C25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E25" s="14" t="s">
-        <v>121</v>
+        <v>118</v>
+      </c>
+      <c r="F25" s="2" t="str" cm="1">
+        <f t="array" ref="F25">IF(SUMPRODUCT(--EXACT(E25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6589,12 +6910,21 @@
       <c r="C26" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="D26" s="2" t="str" cm="1">
+        <f t="array" ref="D26">IF(SUMPRODUCT(--EXACT(C26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E26" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="F26" s="2" t="str" cm="1">
+        <f t="array" ref="F26">IF(SUMPRODUCT(--EXACT(E26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6604,11 +6934,19 @@
       <c r="C27" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="D27" s="2" t="str" cm="1">
+        <f t="array" ref="D27">IF(SUMPRODUCT(--EXACT(C27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="F27" s="2" t="str" cm="1">
+        <f t="array" ref="F27">IF(SUMPRODUCT(--EXACT(E27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6618,11 +6956,19 @@
       <c r="C28" s="3" t="s">
         <v>106</v>
       </c>
+      <c r="D28" s="2" t="str" cm="1">
+        <f t="array" ref="D28">IF(SUMPRODUCT(--EXACT(C28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E28" s="10" t="s">
-        <v>113</v>
+        <v>96</v>
+      </c>
+      <c r="F28" s="2" t="str" cm="1">
+        <f t="array" ref="F28">IF(SUMPRODUCT(--EXACT(E28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6632,11 +6978,19 @@
       <c r="C29" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="D29" s="2" t="str" cm="1">
+        <f t="array" ref="D29">IF(SUMPRODUCT(--EXACT(C29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E29" s="10" t="s">
-        <v>92</v>
+        <v>128</v>
+      </c>
+      <c r="F29" s="2" t="str" cm="1">
+        <f t="array" ref="F29">IF(SUMPRODUCT(--EXACT(E29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6646,11 +7000,19 @@
       <c r="C30" s="13" t="s">
         <v>107</v>
       </c>
+      <c r="D30" s="2" t="str" cm="1">
+        <f t="array" ref="D30">IF(SUMPRODUCT(--EXACT(C30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E30" s="10" t="s">
-        <v>143</v>
+        <v>103</v>
+      </c>
+      <c r="F30" s="2" t="str" cm="1">
+        <f t="array" ref="F30">IF(SUMPRODUCT(--EXACT(E30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6660,11 +7022,19 @@
       <c r="C31" s="13" t="s">
         <v>144</v>
       </c>
+      <c r="D31" s="2" t="str" cm="1">
+        <f t="array" ref="D31">IF(SUMPRODUCT(--EXACT(C31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E31" s="10" t="s">
-        <v>96</v>
+        <v>87</v>
+      </c>
+      <c r="F31" s="2" t="str" cm="1">
+        <f t="array" ref="F31">IF(SUMPRODUCT(--EXACT(E31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6674,11 +7044,19 @@
       <c r="C32" s="3" t="s">
         <v>108</v>
       </c>
+      <c r="D32" s="2" t="str" cm="1">
+        <f t="array" ref="D32">IF(SUMPRODUCT(--EXACT(C32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E32" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="F32" s="2" t="str" cm="1">
+        <f t="array" ref="F32">IF(SUMPRODUCT(--EXACT(E32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6688,11 +7066,19 @@
       <c r="C33" s="3" t="s">
         <v>128</v>
       </c>
+      <c r="D33" s="2" t="str" cm="1">
+        <f t="array" ref="D33">IF(SUMPRODUCT(--EXACT(C33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
       <c r="E33" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
+      </c>
+      <c r="F33" s="2" t="str" cm="1">
+        <f t="array" ref="F33">IF(SUMPRODUCT(--EXACT(E33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6702,8 +7088,13 @@
       <c r="C34" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">IF(SUMPRODUCT(--EXACT(C34,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6713,8 +7104,13 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="D35" s="2" t="str" cm="1">
+        <f t="array" ref="D35">IF(SUMPRODUCT(--EXACT(C35,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6722,10 +7118,15 @@
         <v>230</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D36" s="2" t="str" cm="1">
+        <f t="array" ref="D36">IF(SUMPRODUCT(--EXACT(C36,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6733,36 +7134,42 @@
         <v>231</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>243</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D37" s="2" t="str" cm="1">
+        <f t="array" ref="D37">IF(SUMPRODUCT(--EXACT(C37,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="F37" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="N1:O14" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:O14">
-      <sortCondition descending="1" ref="O1:O14"/>
+  <autoFilter ref="R1:S14" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S14">
+      <sortCondition descending="1" ref="S1:S14"/>
     </sortState>
   </autoFilter>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{E4A41900-CC37-48F7-B004-B74485AD8A27}">
       <formula1>$C$2:$C$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F17" xr:uid="{D2957299-AA86-4AAC-BC70-7E025FFACDDE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G17 H10:H17" xr:uid="{D2957299-AA86-4AAC-BC70-7E025FFACDDE}">
       <formula1>$E$2:$E$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G9" xr:uid="{AA5AA722-50BA-410B-82F7-991D269DC6F9}">
-      <formula1>$F$2:$F$17</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I9 J6:J9" xr:uid="{AA5AA722-50BA-410B-82F7-991D269DC6F9}">
+      <formula1>$G$2:$G$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{17203C8A-B2E7-44D3-841C-07C49EEA4C15}">
-      <formula1>$G$2:$G$9</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K5 L4:L5" xr:uid="{17203C8A-B2E7-44D3-841C-07C49EEA4C15}">
+      <formula1>$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{F97D354B-0CFA-40AB-AC95-3381B40D6483}">
-      <formula1>$H$2:$H$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M3" xr:uid="{F97D354B-0CFA-40AB-AC95-3381B40D6483}">
+      <formula1>$K$2:$K$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{F67376F6-AFA2-466D-BFF5-DCCAE0FB3ECB}">
-      <formula1>$I$2:$I$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{F67376F6-AFA2-466D-BFF5-DCCAE0FB3ECB}">
+      <formula1>$M$2:$M$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -7325,7 +7732,7 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
@@ -7333,43 +7740,43 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX2">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY2">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ2">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA2">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO2)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP2)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO2)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP2)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB2">
-        <f>IF(BQ2='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ2='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC2">
-        <f>IF(BS2='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS2='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD2">
-        <f>IFERROR(VLOOKUP(BT2,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT2,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE2">
-        <f>IF(BR2='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR2='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>48.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.25">
@@ -7588,7 +7995,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
@@ -7596,38 +8003,38 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY3">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ3">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA3">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO3)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP3)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO3)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP3)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB3">
-        <f>IF(BQ3='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ3='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC3">
-        <f>IF(BS3='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS3='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD3">
-        <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE3">
-        <f>IF(BR3='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR3='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF3" s="7">
@@ -7851,7 +8258,7 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
@@ -7859,38 +8266,38 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX4">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY4">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ4">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA4">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO4)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP4)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO4)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP4)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB4">
-        <f>IF(BQ4='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ4='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC4">
-        <f>IF(BS4='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS4='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD4">
-        <f>IFERROR(VLOOKUP(BT4,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT4,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE4">
-        <f>IF(BR4='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR4='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF4" s="7">
@@ -8114,51 +8521,51 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX5">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY5">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ5">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA5">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO5)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP5)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO5)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP5)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB5">
-        <f>IF(BQ5='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ5='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC5">
-        <f>IF(BS5='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS5='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD5">
-        <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE5">
-        <f>IF(BR5='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR5='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.25">
@@ -8377,7 +8784,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
@@ -8385,43 +8792,43 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY6">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ6">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA6">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO6)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP6)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO6)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP6)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB6">
-        <f>IF(BQ6='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ6='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC6">
-        <f>IF(BS6='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS6='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD6">
-        <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE6">
-        <f>IF(BR6='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR6='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8640,7 +9047,7 @@
       </c>
       <c r="BU7">
         <f>IF(C7='Resultats Reals'!$C$2,2,IF(OR(C7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C7)&gt;0),1,0))+IF(D7='Resultats Reals'!$C$5,2,IF(OR(D7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D7)&gt;0),1,0))+IF(E7='Resultats Reals'!$C$8,2,IF(OR(E7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E7)&gt;0),1,0))+IF(F7='Resultats Reals'!$C$11,2,IF(OR(F7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F7)&gt;0),1,0))+IF(G7='Resultats Reals'!$C$14,2,IF(OR(G7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G7)&gt;0),1,0))+IF(H7='Resultats Reals'!$C$17,2,IF(OR(H7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H7)&gt;0),1,0))+IF(I7='Resultats Reals'!$C$20,2,IF(OR(I7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I7)&gt;0),1,0))+IF(J7='Resultats Reals'!$C$23,2,IF(OR(J7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J7)&gt;0),1,0))+IF(K7='Resultats Reals'!$C$26,2,IF(OR(K7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K7)&gt;0),1,0))+IF(L7='Resultats Reals'!$C$29,2,IF(OR(L7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L7)&gt;0),1,0))+IF(M7='Resultats Reals'!$C$32,2,IF(OR(M7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M7)&gt;0),1,0))+IF(N7='Resultats Reals'!$C$35,2,IF(OR(N7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N7)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z7)&gt;0),1,0))</f>
@@ -8648,38 +9055,38 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY7">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ7">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA7">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO7)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP7)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO7)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP7)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB7">
-        <f>IF(BQ7='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ7='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC7">
-        <f>IF(BS7='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS7='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD7">
-        <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE7">
-        <f>IF(BR7='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR7='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF7" s="7">
@@ -8903,7 +9310,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N8)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
@@ -8911,43 +9318,43 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BX8">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY8">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ8">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA8">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO8)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP8)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO8)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP8)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB8">
-        <f>IF(BQ8='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ8='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC8">
-        <f>IF(BS8='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS8='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD8">
-        <f>IFERROR(VLOOKUP(BT8,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT8,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE8">
-        <f>IF(BR8='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR8='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.25">
@@ -9169,51 +9576,51 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N9)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z9)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX9">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY9">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ9">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA9">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO9)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP9)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO9)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP9)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB9">
-        <f>IF(BQ9='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ9='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC9">
-        <f>IF(BS9='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS9='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD9">
-        <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE9">
-        <f>IF(BR9='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR9='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.25">
@@ -9432,51 +9839,51 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX10">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY10">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ10">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA10">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO10)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP10)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO10)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP10)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB10">
-        <f>IF(BQ10='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ10='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC10">
-        <f>IF(BS10='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS10='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD10">
-        <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE10">
-        <f>IF(BR10='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR10='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
@@ -9695,7 +10102,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
@@ -9703,43 +10110,43 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX11">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY11">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ11">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA11">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO11)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP11)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO11)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP11)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB11">
-        <f>IF(BQ11='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ11='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC11">
-        <f>IF(BS11='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS11='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD11">
-        <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE11">
-        <f>IF(BR11='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR11='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
@@ -9962,42 +10369,42 @@
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX12">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY12">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ12">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA12">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO12)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP12)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO12)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP12)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB12">
-        <f>IF(BQ12='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ12='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC12">
-        <f>IF(BS12='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS12='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD12">
-        <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE12">
-        <f>IF(BR12='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR12='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF12" s="7">
@@ -10221,51 +10628,51 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY13">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ13">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA13">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO13)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP13)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO13)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP13)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB13">
-        <f>IF(BQ13='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ13='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC13">
-        <f>IF(BS13='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS13='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD13">
-        <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE13">
-        <f>IF(BR13='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR13='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.25">
@@ -10484,51 +10891,51 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX14">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY14">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ14">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA14">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO14)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP14)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO14)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP14)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB14">
-        <f>IF(BQ14='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ14='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC14">
-        <f>IF(BS14='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS14='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD14">
-        <f>IFERROR(VLOOKUP(BT14,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT14,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE14">
-        <f>IF(BR14='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR14='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.25">
@@ -10747,46 +11154,46 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
         <v>11.5</v>
       </c>
       <c r="BX15">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY15">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ15">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA15">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO15)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP15)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO15)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP15)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB15">
-        <f>IF(BQ15='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ15='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC15">
-        <f>IF(BS15='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS15='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD15">
-        <f>IFERROR(VLOOKUP(BT15,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT15,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE15">
-        <f>IF(BR15='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR15='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF15" s="7">
@@ -11010,7 +11417,7 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
@@ -11018,43 +11425,43 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BX16">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY16">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ16">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA16">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO16)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP16)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO16)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP16)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB16">
-        <f>IF(BQ16='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ16='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC16">
-        <f>IF(BS16='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS16='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD16">
-        <f>IFERROR(VLOOKUP(BT16,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT16,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE16">
-        <f>IF(BR16='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR16='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.25">
@@ -11273,7 +11680,7 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N17)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
@@ -11281,43 +11688,43 @@
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX17">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY17">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ17">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA17">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO17)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP17)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO17)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP17)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB17">
-        <f>IF(BQ17='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ17='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC17">
-        <f>IF(BS17='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS17='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD17">
-        <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE17">
-        <f>IF(BR17='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR17='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.25">
@@ -11539,7 +11946,7 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
@@ -11547,43 +11954,43 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX18">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY18">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ18">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA18">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO18)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP18)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO18)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP18)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB18">
-        <f>IF(BQ18='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ18='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC18">
-        <f>IF(BS18='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS18='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD18">
-        <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE18">
-        <f>IF(BR18='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR18='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
@@ -11802,51 +12209,51 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY19">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ19">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA19">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO19)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP19)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO19)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP19)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB19">
-        <f>IF(BQ19='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ19='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC19">
-        <f>IF(BS19='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS19='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD19">
-        <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE19">
-        <f>IF(BR19='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR19='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.25">
@@ -12065,7 +12472,7 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
@@ -12073,43 +12480,43 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX20">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY20">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ20">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA20">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO20)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP20)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO20)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP20)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB20">
-        <f>IF(BQ20='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ20='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC20">
-        <f>IF(BS20='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS20='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD20">
-        <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE20">
-        <f>IF(BR20='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR20='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
@@ -12328,51 +12735,51 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX21">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY21">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ21">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA21">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO21)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP21)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO21)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP21)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB21">
-        <f>IF(BQ21='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ21='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC21">
-        <f>IF(BS21='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS21='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD21">
-        <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE21">
-        <f>IF(BR21='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR21='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.25">
@@ -12595,42 +13002,42 @@
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX22">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY22">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ22">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA22">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO22)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP22)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO22)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP22)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB22">
-        <f>IF(BQ22='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ22='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC22">
-        <f>IF(BS22='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS22='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD22">
-        <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE22">
-        <f>IF(BR22='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR22='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF22" s="7">
@@ -12858,42 +13265,42 @@
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX23">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY23">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ23">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA23">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO23)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP23)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO23)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP23)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB23">
-        <f>IF(BQ23='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ23='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC23">
-        <f>IF(BS23='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS23='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD23">
-        <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE23">
-        <f>IF(BR23='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR23='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF23" s="7">
@@ -13117,7 +13524,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
@@ -13125,43 +13532,43 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX24">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY24">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ24">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA24">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO24)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP24)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO24)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP24)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB24">
-        <f>IF(BQ24='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ24='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC24">
-        <f>IF(BS24='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS24='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD24">
-        <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE24">
-        <f>IF(BR24='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR24='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
@@ -13384,42 +13791,42 @@
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX25">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY25">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ25">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA25">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO25)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP25)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO25)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP25)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB25">
-        <f>IF(BQ25='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ25='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC25">
-        <f>IF(BS25='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS25='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD25">
-        <f>IFERROR(VLOOKUP(BT25,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT25,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE25">
-        <f>IF(BR25='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR25='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF25" s="7">
@@ -13646,7 +14053,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
@@ -13657,40 +14064,40 @@
         <v>8.5</v>
       </c>
       <c r="BX26">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY26">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ26">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA26">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO26)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP26)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO26)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP26)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB26">
-        <f>IF(BQ26='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ26='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC26">
-        <f>IF(BS26='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS26='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD26">
-        <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE26">
-        <f>IF(BR26='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR26='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
@@ -13909,51 +14316,51 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX27">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY27">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ27">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA27">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO27)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP27)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO27)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP27)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB27">
-        <f>IF(BQ27='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ27='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC27">
-        <f>IF(BS27='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS27='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD27">
-        <f>IFERROR(VLOOKUP(BT27,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT27,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE27">
-        <f>IF(BR27='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR27='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.25">
@@ -14172,7 +14579,7 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N28)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z28)&gt;0),1,0))</f>
@@ -14180,38 +14587,38 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX28">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY28">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ28">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA28">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO28)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP28)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO28)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP28)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB28">
-        <f>IF(BQ28='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ28='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC28">
-        <f>IF(BS28='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS28='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD28">
-        <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE28">
-        <f>IF(BR28='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR28='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF28" s="7">
@@ -14438,51 +14845,51 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX29">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY29">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ29">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA29">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO29)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP29)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO29)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP29)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB29">
-        <f>IF(BQ29='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ29='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC29">
-        <f>IF(BS29='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS29='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD29">
-        <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE29">
-        <f>IF(BR29='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR29='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.25">
@@ -14701,7 +15108,7 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
@@ -14709,43 +15116,43 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BX30">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY30">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ30">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA30">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO30)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP30)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO30)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP30)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB30">
-        <f>IF(BQ30='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ30='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC30">
-        <f>IF(BS30='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS30='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD30">
-        <f>IFERROR(VLOOKUP(BT30,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT30,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE30">
-        <f>IF(BR30='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR30='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.25">
@@ -14964,51 +15371,51 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX31">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY31">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ31">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA31">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO31)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP31)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO31)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP31)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB31">
-        <f>IF(BQ31='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ31='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC31">
-        <f>IF(BS31='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS31='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD31">
-        <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE31">
-        <f>IF(BR31='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR31='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
@@ -15230,51 +15637,51 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX32">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY32">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ32">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA32">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO32)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP32)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO32)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP32)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB32">
-        <f>IF(BQ32='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ32='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC32">
-        <f>IF(BS32='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS32='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD32">
-        <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE32">
-        <f>IF(BR32='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR32='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
@@ -15496,51 +15903,51 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX33">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY33">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ33">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA33">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO33)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP33)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO33)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP33)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB33">
-        <f>IF(BQ33='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ33='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC33">
-        <f>IF(BS33='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS33='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD33">
-        <f>IFERROR(VLOOKUP(BT33,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT33,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE33">
-        <f>IF(BR33='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR33='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.25">
@@ -15762,51 +16169,51 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX34">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY34">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ34">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA34">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO34)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP34)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO34)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP34)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB34">
-        <f>IF(BQ34='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ34='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC34">
-        <f>IF(BS34='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS34='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD34">
-        <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE34">
-        <f>IF(BR34='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR34='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
@@ -16025,51 +16432,51 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX35">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY35">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ35">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA35">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO35)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP35)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO35)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP35)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB35">
-        <f>IF(BQ35='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ35='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC35">
-        <f>IF(BS35='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS35='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD35">
-        <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE35">
-        <f>IF(BR35='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR35='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.25">
@@ -16288,51 +16695,51 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N36)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z36)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX36">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY36">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ36">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA36">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO36)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP36)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO36)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP36)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB36">
-        <f>IF(BQ36='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ36='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC36">
-        <f>IF(BS36='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS36='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD36">
-        <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE36">
-        <f>IF(BR36='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR36='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.25">
@@ -16551,7 +16958,7 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
@@ -16559,43 +16966,43 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX37">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY37">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ37">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA37">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO37)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP37)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO37)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP37)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB37">
-        <f>IF(BQ37='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ37='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC37">
-        <f>IF(BS37='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS37='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD37">
-        <f>IFERROR(VLOOKUP(BT37,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT37,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE37">
-        <f>IF(BR37='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR37='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.25">
@@ -16817,7 +17224,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
@@ -16825,43 +17232,43 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX38">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY38">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ38">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA38">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO38)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP38)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO38)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP38)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB38">
-        <f>IF(BQ38='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ38='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC38">
-        <f>IF(BS38='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS38='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD38">
-        <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE38">
-        <f>IF(BR38='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR38='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
@@ -17083,51 +17490,51 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N39)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX39">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY39">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ39">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA39">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO39)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP39)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO39)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP39)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB39">
-        <f>IF(BQ39='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ39='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC39">
-        <f>IF(BS39='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS39='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD39">
-        <f>IFERROR(VLOOKUP(BT39,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT39,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE39">
-        <f>IF(BR39='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR39='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.25">
@@ -17353,47 +17760,47 @@
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z40)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX40">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY40">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ40">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA40">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO40)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP40)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO40)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP40)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB40">
-        <f>IF(BQ40='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ40='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC40">
-        <f>IF(BS40='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS40='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD40">
-        <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE40">
-        <f>IF(BR40='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR40='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
@@ -17612,51 +18019,51 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N41)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX41">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY41">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ41">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA41">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO41)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP41)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO41)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP41)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB41">
-        <f>IF(BQ41='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ41='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC41">
-        <f>IF(BS41='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS41='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD41">
-        <f>IFERROR(VLOOKUP(BT41,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT41,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE41">
-        <f>IF(BR41='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR41='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.25">
@@ -17875,51 +18282,51 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N42)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z42)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX42">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY42">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ42">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA42">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO42)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP42)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO42)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP42)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB42">
-        <f>IF(BQ42='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ42='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC42">
-        <f>IF(BS42='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS42='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD42">
-        <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE42">
-        <f>IF(BR42='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR42='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.25">
@@ -18141,51 +18548,51 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N43)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z43)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX43">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY43">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ43">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA43">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO43)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP43)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO43)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP43)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB43">
-        <f>IF(BQ43='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ43='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC43">
-        <f>IF(BS43='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS43='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD43">
-        <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE43">
-        <f>IF(BR43='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR43='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.25">
@@ -18404,51 +18811,51 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N44)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z44)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BX44">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY44">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ44">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA44">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO44)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP44)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO44)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP44)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB44">
-        <f>IF(BQ44='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ44='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC44">
-        <f>IF(BS44='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS44='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD44">
-        <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE44">
-        <f>IF(BR44='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR44='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>52.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.25">
@@ -18667,7 +19074,7 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N45)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z45)&gt;0),1,0))</f>
@@ -18675,43 +19082,43 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX45">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY45">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ45">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA45">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO45)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP45)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO45)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP45)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB45">
-        <f>IF(BQ45='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ45='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC45">
-        <f>IF(BS45='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS45='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD45">
-        <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE45">
-        <f>IF(BR45='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR45='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.25">
@@ -18933,51 +19340,51 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N46)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z46)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BX46">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY46">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ46">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA46">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO46)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP46)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO46)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP46)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB46">
-        <f>IF(BQ46='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ46='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC46">
-        <f>IF(BS46='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS46='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD46">
-        <f>IFERROR(VLOOKUP(BT46,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT46,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE46">
-        <f>IF(BR46='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR46='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.25">
@@ -19204,43 +19611,43 @@
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX47">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY47">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ47">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA47">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO47)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP47)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO47)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP47)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB47">
-        <f>IF(BQ47='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ47='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC47">
-        <f>IF(BS47='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS47='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD47">
-        <f>IFERROR(VLOOKUP(BT47,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT47,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE47">
-        <f>IF(BR47='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR47='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.25">
@@ -19459,51 +19866,51 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N48)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z48)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX48">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY48">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ48">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA48">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO48)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP48)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO48)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP48)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB48">
-        <f>IF(BQ48='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ48='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC48">
-        <f>IF(BS48='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS48='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD48">
-        <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE48">
-        <f>IF(BR48='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR48='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.25">
@@ -19725,51 +20132,51 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N49)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z49)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX49">
-        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY49">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ49">
-        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA49">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO49)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP49)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO49)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP49)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB49">
-        <f>IF(BQ49='Resultats Reals'!$J$2,5,0)</f>
+        <f>IF(BQ49='Resultats Reals'!$N$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC49">
-        <f>IF(BS49='Resultats Reals'!$K$2,5,0)</f>
+        <f>IF(BS49='Resultats Reals'!$O$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD49">
-        <f>IFERROR(VLOOKUP(BT49,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT49,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE49">
-        <f>IF(BR49='Resultats Reals'!$L$2,5,0)</f>
+        <f>IF(BR49='Resultats Reals'!$P$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -19788,10 +20195,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" t="s">
         <v>244</v>
-      </c>
-      <c r="B1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -20180,7 +20587,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B50">
         <v>1906</v>
@@ -20194,7 +20601,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -20242,7 +20649,7 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -20433,11 +20840,6 @@
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33CCDFAC-495C-4070-89CE-2F6978D2A099}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB7B02F-D8FD-42C3-A0F7-CEB028CB1E06}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gràfics!$A$1:$B$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$R$1:$S$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$N$1:$O$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3804" uniqueCount="249">
   <si>
     <t>Participants</t>
   </si>
@@ -808,7 +808,10 @@
     <t>Bòsnia i Hercegovina</t>
   </si>
   <si>
-    <t>Verificació Països</t>
+    <t>Verificació Països Grups</t>
+  </si>
+  <si>
+    <t>Verificació setzens</t>
   </si>
 </sst>
 </file>
@@ -933,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -958,7 +961,6 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,10 +976,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6043,33 +6041,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6079,53 +6070,38 @@
       <c r="C1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>247</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>247</v>
+      <c r="F1" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>247</v>
+        <v>222</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>247</v>
+        <v>224</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>224</v>
+        <v>70</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="S1" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6135,58 +6111,38 @@
       <c r="C2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="2" t="str" cm="1">
-        <f t="array" ref="D2">IF(SUMPRODUCT(--EXACT(C2,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E2" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="2" t="str" cm="1">
-        <f t="array" ref="F2">IF(SUMPRODUCT(--EXACT(E2,C2:C37))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F2" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H2" s="2" t="str" cm="1">
-        <f t="array" ref="H2">IF(SUMPRODUCT(--EXACT(G2,E2:E37))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
+      <c r="H2" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J2" s="2" t="str" cm="1">
-        <f t="array" ref="J2">IF(SUMPRODUCT(--EXACT(I2,G2:G37))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="J2" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="L2" s="2" t="str" cm="1">
-        <f t="array" ref="L2">IF(SUMPRODUCT(--EXACT(K2,I2:I37))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="N2" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="N2" t="s">
         <v>158</v>
       </c>
-      <c r="S2" s="3">
+      <c r="O2" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6196,49 +6152,29 @@
       <c r="C3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="2" t="str" cm="1">
-        <f t="array" ref="D3">IF(SUMPRODUCT(--EXACT(C3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E3" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="2" t="str" cm="1">
-        <f t="array" ref="F3">IF(SUMPRODUCT(--EXACT(E3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F3" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="str" cm="1">
-        <f t="array" ref="H3">IF(SUMPRODUCT(--EXACT(G3,E3:E38))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
+      <c r="H3" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="2" t="str" cm="1">
-        <f t="array" ref="J3">IF(SUMPRODUCT(--EXACT(I3,G3:G38))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="L3" s="2" t="str" cm="1">
-        <f t="array" ref="L3">IF(SUMPRODUCT(--EXACT(K3,I3:I38))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="N3" t="s">
         <v>162</v>
       </c>
-      <c r="S3" s="3">
+      <c r="O3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6248,43 +6184,26 @@
       <c r="C4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="2" t="str" cm="1">
-        <f t="array" ref="D4">IF(SUMPRODUCT(--EXACT(C4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E4" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="2" t="str" cm="1">
-        <f t="array" ref="F4">IF(SUMPRODUCT(--EXACT(E4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F4" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="2" t="str" cm="1">
-        <f t="array" ref="H4">IF(SUMPRODUCT(--EXACT(G4,E4:E39))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J4" s="2" t="str" cm="1">
-        <f t="array" ref="J4">IF(SUMPRODUCT(--EXACT(I4,G4:G39))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="L4" s="16"/>
-      <c r="R4" t="s">
+      <c r="N4" t="s">
         <v>155</v>
       </c>
-      <c r="S4" s="3">
+      <c r="O4" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6294,43 +6213,26 @@
       <c r="C5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="2" t="str" cm="1">
-        <f t="array" ref="D5">IF(SUMPRODUCT(--EXACT(C5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="2" t="str" cm="1">
-        <f t="array" ref="F5">IF(SUMPRODUCT(--EXACT(E5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F5" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H5" s="2" t="str" cm="1">
-        <f t="array" ref="H5">IF(SUMPRODUCT(--EXACT(G5,E5:E40))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J5" s="2" t="str" cm="1">
-        <f t="array" ref="J5">IF(SUMPRODUCT(--EXACT(I5,G5:G40))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="L5" s="16"/>
-      <c r="R5" t="s">
+      <c r="N5" t="s">
         <v>129</v>
       </c>
-      <c r="S5" s="3">
+      <c r="O5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6340,36 +6242,23 @@
       <c r="C6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="2" t="str" cm="1">
-        <f t="array" ref="D6">IF(SUMPRODUCT(--EXACT(C6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E6" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="2" t="str" cm="1">
-        <f t="array" ref="F6">IF(SUMPRODUCT(--EXACT(E6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F6" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H6" s="2" t="str" cm="1">
-        <f t="array" ref="H6">IF(SUMPRODUCT(--EXACT(G6,E6:E41))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="J6" s="16"/>
-      <c r="R6" t="s">
+      <c r="N6" t="s">
         <v>167</v>
       </c>
-      <c r="S6" s="3">
+      <c r="O6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6379,36 +6268,23 @@
       <c r="C7" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="2" t="str" cm="1">
-        <f t="array" ref="D7">IF(SUMPRODUCT(--EXACT(C7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="2" t="str" cm="1">
-        <f t="array" ref="F7">IF(SUMPRODUCT(--EXACT(E7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F7" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H7" s="2" t="str" cm="1">
-        <f t="array" ref="H7">IF(SUMPRODUCT(--EXACT(G7,E7:E42))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="J7" s="16"/>
-      <c r="R7" t="s">
+      <c r="N7" t="s">
         <v>195</v>
       </c>
-      <c r="S7" s="3">
+      <c r="O7" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6418,36 +6294,23 @@
       <c r="C8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="2" t="str" cm="1">
-        <f t="array" ref="D8">IF(SUMPRODUCT(--EXACT(C8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="2" t="str" cm="1">
-        <f t="array" ref="F8">IF(SUMPRODUCT(--EXACT(E8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F8" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H8" s="2" t="str" cm="1">
-        <f t="array" ref="H8">IF(SUMPRODUCT(--EXACT(G8,E8:E43))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="J8" s="16"/>
-      <c r="R8" t="s">
+      <c r="N8" t="s">
         <v>212</v>
       </c>
-      <c r="S8" s="3">
+      <c r="O8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6457,36 +6320,23 @@
       <c r="C9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="2" t="str" cm="1">
-        <f t="array" ref="D9">IF(SUMPRODUCT(--EXACT(C9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E9" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="2" t="str" cm="1">
-        <f t="array" ref="F9">IF(SUMPRODUCT(--EXACT(E9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
+      <c r="F9" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H9" s="2" t="str" cm="1">
-        <f t="array" ref="H9">IF(SUMPRODUCT(--EXACT(G9,E9:E44))&gt;0,"OK","Revisar")</f>
-        <v>Revisar</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="R9" t="s">
+      <c r="N9" t="s">
         <v>146</v>
       </c>
-      <c r="S9" s="3">
+      <c r="O9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6496,29 +6346,20 @@
       <c r="C10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="2" t="str" cm="1">
-        <f t="array" ref="D10">IF(SUMPRODUCT(--EXACT(C10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E10" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="2" t="str" cm="1">
-        <f t="array" ref="F10">IF(SUMPRODUCT(--EXACT(E10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="R10" t="s">
+      <c r="N10" t="s">
         <v>122</v>
       </c>
-      <c r="S10" s="3">
+      <c r="O10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6528,29 +6369,20 @@
       <c r="C11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="2" t="str" cm="1">
-        <f t="array" ref="D11">IF(SUMPRODUCT(--EXACT(C11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="2" t="str" cm="1">
-        <f t="array" ref="F11">IF(SUMPRODUCT(--EXACT(E11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H11" s="16"/>
-      <c r="R11" t="s">
+      <c r="N11" t="s">
         <v>123</v>
       </c>
-      <c r="S11" s="3">
+      <c r="O11" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6560,29 +6392,20 @@
       <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="2" t="str" cm="1">
-        <f t="array" ref="D12">IF(SUMPRODUCT(--EXACT(C12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E12" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="2" t="str" cm="1">
-        <f t="array" ref="F12">IF(SUMPRODUCT(--EXACT(E12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="R12" t="s">
+      <c r="N12" t="s">
         <v>134</v>
       </c>
-      <c r="S12" s="3">
+      <c r="O12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6592,29 +6415,20 @@
       <c r="C13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="2" t="str" cm="1">
-        <f t="array" ref="D13">IF(SUMPRODUCT(--EXACT(C13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E13" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="2" t="str" cm="1">
-        <f t="array" ref="F13">IF(SUMPRODUCT(--EXACT(E13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="R13" t="s">
+      <c r="N13" t="s">
         <v>133</v>
       </c>
-      <c r="S13" s="3">
+      <c r="O13" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6624,29 +6438,20 @@
       <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="2" t="str" cm="1">
-        <f t="array" ref="D14">IF(SUMPRODUCT(--EXACT(C14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E14" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="2" t="str" cm="1">
-        <f t="array" ref="F14">IF(SUMPRODUCT(--EXACT(E14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="R14" t="s">
+      <c r="N14" t="s">
         <v>201</v>
       </c>
-      <c r="S14" s="3">
+      <c r="O14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6656,23 +6461,14 @@
       <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="2" t="str" cm="1">
-        <f t="array" ref="D15">IF(SUMPRODUCT(--EXACT(C15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E15" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="2" t="str" cm="1">
-        <f t="array" ref="F15">IF(SUMPRODUCT(--EXACT(E15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6682,23 +6478,14 @@
       <c r="C16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="2" t="str" cm="1">
-        <f t="array" ref="D16">IF(SUMPRODUCT(--EXACT(C16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E16" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="2" t="str" cm="1">
-        <f t="array" ref="F16">IF(SUMPRODUCT(--EXACT(E16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6708,23 +6495,14 @@
       <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="2" t="str" cm="1">
-        <f t="array" ref="D17">IF(SUMPRODUCT(--EXACT(C17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E17" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="2" t="str" cm="1">
-        <f t="array" ref="F17">IF(SUMPRODUCT(--EXACT(E17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6734,19 +6512,11 @@
       <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="2" t="str" cm="1">
-        <f t="array" ref="D18">IF(SUMPRODUCT(--EXACT(C18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E18" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="2" t="str" cm="1">
-        <f t="array" ref="F18">IF(SUMPRODUCT(--EXACT(E18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6756,19 +6526,11 @@
       <c r="C19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="2" t="str" cm="1">
-        <f t="array" ref="D19">IF(SUMPRODUCT(--EXACT(C19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E19" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="2" t="str" cm="1">
-        <f t="array" ref="F19">IF(SUMPRODUCT(--EXACT(E19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6778,19 +6540,11 @@
       <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="2" t="str" cm="1">
-        <f t="array" ref="D20">IF(SUMPRODUCT(--EXACT(C20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="2" t="str" cm="1">
-        <f t="array" ref="F20">IF(SUMPRODUCT(--EXACT(E20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6800,19 +6554,11 @@
       <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="2" t="str" cm="1">
-        <f t="array" ref="D21">IF(SUMPRODUCT(--EXACT(C21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E21" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="2" t="str" cm="1">
-        <f t="array" ref="F21">IF(SUMPRODUCT(--EXACT(E21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6822,19 +6568,11 @@
       <c r="C22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="2" t="str" cm="1">
-        <f t="array" ref="D22">IF(SUMPRODUCT(--EXACT(C22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E22" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F22" s="2" t="str" cm="1">
-        <f t="array" ref="F22">IF(SUMPRODUCT(--EXACT(E22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6844,19 +6582,11 @@
       <c r="C23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="2" t="str" cm="1">
-        <f t="array" ref="D23">IF(SUMPRODUCT(--EXACT(C23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E23" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="2" t="str" cm="1">
-        <f t="array" ref="F23">IF(SUMPRODUCT(--EXACT(E23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6866,19 +6596,11 @@
       <c r="C24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="2" t="str" cm="1">
-        <f t="array" ref="D24">IF(SUMPRODUCT(--EXACT(C24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E24" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="2" t="str" cm="1">
-        <f t="array" ref="F24">IF(SUMPRODUCT(--EXACT(E24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6888,19 +6610,11 @@
       <c r="C25" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="2" t="str" cm="1">
-        <f t="array" ref="D25">IF(SUMPRODUCT(--EXACT(C25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E25" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="2" t="str" cm="1">
-        <f t="array" ref="F25">IF(SUMPRODUCT(--EXACT(E25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6910,21 +6624,12 @@
       <c r="C26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="2" t="str" cm="1">
-        <f t="array" ref="D26">IF(SUMPRODUCT(--EXACT(C26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E26" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="2" t="str" cm="1">
-        <f t="array" ref="F26">IF(SUMPRODUCT(--EXACT(E26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="16"/>
+      <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6934,19 +6639,11 @@
       <c r="C27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="2" t="str" cm="1">
-        <f t="array" ref="D27">IF(SUMPRODUCT(--EXACT(C27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="2" t="str" cm="1">
-        <f t="array" ref="F27">IF(SUMPRODUCT(--EXACT(E27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6956,19 +6653,11 @@
       <c r="C28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="2" t="str" cm="1">
-        <f t="array" ref="D28">IF(SUMPRODUCT(--EXACT(C28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E28" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F28" s="2" t="str" cm="1">
-        <f t="array" ref="F28">IF(SUMPRODUCT(--EXACT(E28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6978,19 +6667,11 @@
       <c r="C29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="2" t="str" cm="1">
-        <f t="array" ref="D29">IF(SUMPRODUCT(--EXACT(C29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E29" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="2" t="str" cm="1">
-        <f t="array" ref="F29">IF(SUMPRODUCT(--EXACT(E29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -7000,19 +6681,11 @@
       <c r="C30" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="2" t="str" cm="1">
-        <f t="array" ref="D30">IF(SUMPRODUCT(--EXACT(C30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E30" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="2" t="str" cm="1">
-        <f t="array" ref="F30">IF(SUMPRODUCT(--EXACT(E30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -7022,19 +6695,11 @@
       <c r="C31" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="2" t="str" cm="1">
-        <f t="array" ref="D31">IF(SUMPRODUCT(--EXACT(C31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E31" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="2" t="str" cm="1">
-        <f t="array" ref="F31">IF(SUMPRODUCT(--EXACT(E31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -7044,19 +6709,11 @@
       <c r="C32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="2" t="str" cm="1">
-        <f t="array" ref="D32">IF(SUMPRODUCT(--EXACT(C32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E32" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F32" s="2" t="str" cm="1">
-        <f t="array" ref="F32">IF(SUMPRODUCT(--EXACT(E32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -7066,19 +6723,11 @@
       <c r="C33" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="2" t="str" cm="1">
-        <f t="array" ref="D33">IF(SUMPRODUCT(--EXACT(C33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
       <c r="E33" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F33" s="2" t="str" cm="1">
-        <f t="array" ref="F33">IF(SUMPRODUCT(--EXACT(E33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -7088,13 +6737,8 @@
       <c r="C34" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="2" t="str" cm="1">
-        <f t="array" ref="D34">IF(SUMPRODUCT(--EXACT(C34,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -7104,13 +6748,8 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="2" t="str" cm="1">
-        <f t="array" ref="D35">IF(SUMPRODUCT(--EXACT(C35,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -7120,13 +6759,8 @@
       <c r="C36" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="2" t="str" cm="1">
-        <f t="array" ref="D36">IF(SUMPRODUCT(--EXACT(C36,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -7136,36 +6770,31 @@
       <c r="C37" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="2" t="str" cm="1">
-        <f t="array" ref="D37">IF(SUMPRODUCT(--EXACT(C37,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
-        <v>OK</v>
-      </c>
-      <c r="F37" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="R1:S14" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S14">
-      <sortCondition descending="1" ref="S1:S14"/>
+  <autoFilter ref="N1:O14" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:O14">
+      <sortCondition descending="1" ref="O1:O14"/>
     </sortState>
   </autoFilter>
   <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G9" xr:uid="{AA5AA722-50BA-410B-82F7-991D269DC6F9}">
+      <formula1>$F$2:$F$17</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{17203C8A-B2E7-44D3-841C-07C49EEA4C15}">
+      <formula1>$G$2:$G$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{F97D354B-0CFA-40AB-AC95-3381B40D6483}">
+      <formula1>$H$2:$H$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{F67376F6-AFA2-466D-BFF5-DCCAE0FB3ECB}">
+      <formula1>$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F17" xr:uid="{D2957299-AA86-4AAC-BC70-7E025FFACDDE}">
+      <formula1>$E$2:$E$33</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{E4A41900-CC37-48F7-B004-B74485AD8A27}">
       <formula1>$C$2:$C$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G17 H10:H17" xr:uid="{D2957299-AA86-4AAC-BC70-7E025FFACDDE}">
-      <formula1>$E$2:$E$33</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I9 J6:J9" xr:uid="{AA5AA722-50BA-410B-82F7-991D269DC6F9}">
-      <formula1>$G$2:$G$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K5 L4:L5" xr:uid="{17203C8A-B2E7-44D3-841C-07C49EEA4C15}">
-      <formula1>$I$2:$I$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M3" xr:uid="{F97D354B-0CFA-40AB-AC95-3381B40D6483}">
-      <formula1>$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{F67376F6-AFA2-466D-BFF5-DCCAE0FB3ECB}">
-      <formula1>$M$2:$M$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7743,35 +7372,35 @@
         <v>12</v>
       </c>
       <c r="BX2">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY2">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ2">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN2)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN2)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA2">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO2)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP2)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO2)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP2)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB2">
-        <f>IF(BQ2='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ2='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC2">
-        <f>IF(BS2='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS2='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD2">
-        <f>IFERROR(VLOOKUP(BT2,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT2,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE2">
-        <f>IF(BR2='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR2='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF2" s="7">
@@ -8006,35 +7635,35 @@
         <v>11.5</v>
       </c>
       <c r="BX3">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY3">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ3">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN3)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN3)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA3">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO3)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP3)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO3)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP3)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB3">
-        <f>IF(BQ3='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ3='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC3">
-        <f>IF(BS3='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS3='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD3">
-        <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE3">
-        <f>IF(BR3='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR3='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF3" s="7">
@@ -8269,35 +7898,35 @@
         <v>8</v>
       </c>
       <c r="BX4">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY4">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ4">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN4)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN4)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA4">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO4)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP4)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO4)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP4)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB4">
-        <f>IF(BQ4='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ4='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC4">
-        <f>IF(BS4='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS4='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD4">
-        <f>IFERROR(VLOOKUP(BT4,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT4,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE4">
-        <f>IF(BR4='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR4='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF4" s="7">
@@ -8532,35 +8161,35 @@
         <v>11</v>
       </c>
       <c r="BX5">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY5">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ5">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN5)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN5)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA5">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO5)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP5)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO5)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP5)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB5">
-        <f>IF(BQ5='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ5='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC5">
-        <f>IF(BS5='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS5='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD5">
-        <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE5">
-        <f>IF(BR5='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR5='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF5" s="7">
@@ -8795,35 +8424,35 @@
         <v>12.5</v>
       </c>
       <c r="BX6">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY6">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ6">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN6)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN6)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA6">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO6)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP6)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO6)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP6)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB6">
-        <f>IF(BQ6='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ6='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC6">
-        <f>IF(BS6='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS6='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD6">
-        <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE6">
-        <f>IF(BR6='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR6='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF6" s="7">
@@ -9058,35 +8687,35 @@
         <v>11.5</v>
       </c>
       <c r="BX7">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY7">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ7">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN7)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN7)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA7">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO7)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP7)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO7)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP7)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB7">
-        <f>IF(BQ7='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ7='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC7">
-        <f>IF(BS7='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS7='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD7">
-        <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE7">
-        <f>IF(BR7='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR7='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF7" s="7">
@@ -9321,35 +8950,35 @@
         <v>6.5</v>
       </c>
       <c r="BX8">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY8">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ8">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN8)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN8)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA8">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO8)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP8)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO8)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP8)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB8">
-        <f>IF(BQ8='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ8='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC8">
-        <f>IF(BS8='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS8='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD8">
-        <f>IFERROR(VLOOKUP(BT8,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT8,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE8">
-        <f>IF(BR8='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR8='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF8" s="7">
@@ -9587,35 +9216,35 @@
         <v>13</v>
       </c>
       <c r="BX9">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY9">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ9">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN9)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN9)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA9">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO9)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP9)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO9)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP9)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB9">
-        <f>IF(BQ9='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ9='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC9">
-        <f>IF(BS9='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS9='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD9">
-        <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE9">
-        <f>IF(BR9='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR9='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF9" s="7">
@@ -9850,35 +9479,35 @@
         <v>13</v>
       </c>
       <c r="BX10">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY10">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ10">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN10)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN10)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA10">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO10)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP10)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO10)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP10)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB10">
-        <f>IF(BQ10='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ10='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC10">
-        <f>IF(BS10='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS10='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD10">
-        <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE10">
-        <f>IF(BR10='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR10='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF10" s="7">
@@ -10113,35 +9742,35 @@
         <v>8</v>
       </c>
       <c r="BX11">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY11">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ11">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN11)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN11)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA11">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO11)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP11)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO11)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP11)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB11">
-        <f>IF(BQ11='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ11='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC11">
-        <f>IF(BS11='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS11='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD11">
-        <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE11">
-        <f>IF(BR11='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR11='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF11" s="7">
@@ -10376,35 +10005,35 @@
         <v>11.5</v>
       </c>
       <c r="BX12">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY12">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ12">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN12)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN12)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA12">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO12)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP12)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO12)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP12)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB12">
-        <f>IF(BQ12='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ12='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC12">
-        <f>IF(BS12='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS12='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD12">
-        <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE12">
-        <f>IF(BR12='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR12='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF12" s="7">
@@ -10639,35 +10268,35 @@
         <v>11.5</v>
       </c>
       <c r="BX13">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY13">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ13">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN13)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN13)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA13">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO13)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP13)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO13)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP13)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB13">
-        <f>IF(BQ13='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ13='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC13">
-        <f>IF(BS13='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS13='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD13">
-        <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE13">
-        <f>IF(BR13='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR13='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF13" s="7">
@@ -10902,35 +10531,35 @@
         <v>13</v>
       </c>
       <c r="BX14">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY14">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ14">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN14)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN14)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA14">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO14)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP14)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO14)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP14)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB14">
-        <f>IF(BQ14='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ14='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC14">
-        <f>IF(BS14='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS14='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD14">
-        <f>IFERROR(VLOOKUP(BT14,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT14,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE14">
-        <f>IF(BR14='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR14='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF14" s="7">
@@ -11165,35 +10794,35 @@
         <v>11.5</v>
       </c>
       <c r="BX15">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY15">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ15">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN15)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN15)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA15">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO15)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP15)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO15)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP15)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB15">
-        <f>IF(BQ15='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ15='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC15">
-        <f>IF(BS15='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS15='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD15">
-        <f>IFERROR(VLOOKUP(BT15,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT15,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE15">
-        <f>IF(BR15='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR15='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF15" s="7">
@@ -11428,35 +11057,35 @@
         <v>9.5</v>
       </c>
       <c r="BX16">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY16">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ16">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN16)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN16)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA16">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO16)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP16)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO16)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP16)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB16">
-        <f>IF(BQ16='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ16='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC16">
-        <f>IF(BS16='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS16='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD16">
-        <f>IFERROR(VLOOKUP(BT16,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT16,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE16">
-        <f>IF(BR16='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR16='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF16" s="7">
@@ -11691,35 +11320,35 @@
         <v>11.5</v>
       </c>
       <c r="BX17">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY17">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ17">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN17)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN17)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA17">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO17)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP17)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO17)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP17)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB17">
-        <f>IF(BQ17='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ17='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC17">
-        <f>IF(BS17='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS17='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD17">
-        <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE17">
-        <f>IF(BR17='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR17='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF17" s="7">
@@ -11957,35 +11586,35 @@
         <v>8.5</v>
       </c>
       <c r="BX18">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY18">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ18">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN18)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN18)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA18">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO18)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP18)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO18)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP18)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB18">
-        <f>IF(BQ18='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ18='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC18">
-        <f>IF(BS18='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS18='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD18">
-        <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE18">
-        <f>IF(BR18='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR18='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF18" s="7">
@@ -12220,35 +11849,35 @@
         <v>10.5</v>
       </c>
       <c r="BX19">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY19">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ19">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN19)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN19)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA19">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO19)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP19)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO19)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP19)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB19">
-        <f>IF(BQ19='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ19='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC19">
-        <f>IF(BS19='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS19='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD19">
-        <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE19">
-        <f>IF(BR19='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR19='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF19" s="7">
@@ -12483,35 +12112,35 @@
         <v>12</v>
       </c>
       <c r="BX20">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY20">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ20">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN20)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN20)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA20">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO20)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP20)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO20)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP20)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB20">
-        <f>IF(BQ20='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ20='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC20">
-        <f>IF(BS20='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS20='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD20">
-        <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE20">
-        <f>IF(BR20='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR20='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF20" s="7">
@@ -12746,35 +12375,35 @@
         <v>12.5</v>
       </c>
       <c r="BX21">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY21">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ21">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN21)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN21)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA21">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO21)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP21)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO21)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP21)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB21">
-        <f>IF(BQ21='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ21='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC21">
-        <f>IF(BS21='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS21='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD21">
-        <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE21">
-        <f>IF(BR21='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR21='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF21" s="7">
@@ -13009,35 +12638,35 @@
         <v>11.5</v>
       </c>
       <c r="BX22">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY22">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ22">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN22)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN22)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA22">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO22)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP22)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO22)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP22)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB22">
-        <f>IF(BQ22='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ22='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC22">
-        <f>IF(BS22='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS22='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD22">
-        <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE22">
-        <f>IF(BR22='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR22='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF22" s="7">
@@ -13272,35 +12901,35 @@
         <v>11.5</v>
       </c>
       <c r="BX23">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY23">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ23">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN23)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN23)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA23">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO23)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP23)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO23)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP23)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB23">
-        <f>IF(BQ23='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ23='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC23">
-        <f>IF(BS23='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS23='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD23">
-        <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE23">
-        <f>IF(BR23='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR23='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF23" s="7">
@@ -13535,35 +13164,35 @@
         <v>14.5</v>
       </c>
       <c r="BX24">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY24">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ24">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN24)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN24)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA24">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO24)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP24)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO24)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP24)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB24">
-        <f>IF(BQ24='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ24='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC24">
-        <f>IF(BS24='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS24='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD24">
-        <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE24">
-        <f>IF(BR24='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR24='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF24" s="7">
@@ -13798,35 +13427,35 @@
         <v>11.5</v>
       </c>
       <c r="BX25">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY25">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ25">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN25)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN25)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA25">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO25)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP25)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO25)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP25)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB25">
-        <f>IF(BQ25='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ25='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC25">
-        <f>IF(BS25='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS25='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD25">
-        <f>IFERROR(VLOOKUP(BT25,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT25,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE25">
-        <f>IF(BR25='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR25='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF25" s="7">
@@ -14064,35 +13693,35 @@
         <v>8.5</v>
       </c>
       <c r="BX26">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY26">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ26">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN26)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN26)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA26">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO26)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP26)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO26)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP26)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB26">
-        <f>IF(BQ26='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ26='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC26">
-        <f>IF(BS26='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS26='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD26">
-        <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE26">
-        <f>IF(BR26='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR26='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF26" s="7">
@@ -14327,35 +13956,35 @@
         <v>12.5</v>
       </c>
       <c r="BX27">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY27">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ27">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN27)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN27)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA27">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO27)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP27)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO27)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP27)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB27">
-        <f>IF(BQ27='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ27='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC27">
-        <f>IF(BS27='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS27='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD27">
-        <f>IFERROR(VLOOKUP(BT27,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT27,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE27">
-        <f>IF(BR27='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR27='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF27" s="7">
@@ -14590,35 +14219,35 @@
         <v>11.5</v>
       </c>
       <c r="BX28">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY28">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ28">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN28)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN28)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA28">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO28)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP28)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO28)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP28)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB28">
-        <f>IF(BQ28='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ28='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC28">
-        <f>IF(BS28='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS28='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD28">
-        <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE28">
-        <f>IF(BR28='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR28='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF28" s="7">
@@ -14856,35 +14485,35 @@
         <v>12</v>
       </c>
       <c r="BX29">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY29">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ29">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN29)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN29)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA29">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO29)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP29)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO29)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP29)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB29">
-        <f>IF(BQ29='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ29='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC29">
-        <f>IF(BS29='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS29='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD29">
-        <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE29">
-        <f>IF(BR29='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR29='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF29" s="7">
@@ -15119,35 +14748,35 @@
         <v>10</v>
       </c>
       <c r="BX30">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY30">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ30">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN30)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN30)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA30">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO30)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP30)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO30)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP30)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB30">
-        <f>IF(BQ30='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ30='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC30">
-        <f>IF(BS30='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS30='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD30">
-        <f>IFERROR(VLOOKUP(BT30,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT30,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE30">
-        <f>IF(BR30='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR30='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF30" s="7">
@@ -15382,35 +15011,35 @@
         <v>13.5</v>
       </c>
       <c r="BX31">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY31">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ31">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN31)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN31)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA31">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO31)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP31)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO31)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP31)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB31">
-        <f>IF(BQ31='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ31='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC31">
-        <f>IF(BS31='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS31='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD31">
-        <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE31">
-        <f>IF(BR31='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR31='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF31" s="7">
@@ -15648,35 +15277,35 @@
         <v>10</v>
       </c>
       <c r="BX32">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY32">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ32">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN32)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN32)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA32">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO32)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP32)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO32)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP32)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB32">
-        <f>IF(BQ32='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ32='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC32">
-        <f>IF(BS32='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS32='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD32">
-        <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE32">
-        <f>IF(BR32='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR32='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF32" s="7">
@@ -15914,35 +15543,35 @@
         <v>12.5</v>
       </c>
       <c r="BX33">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY33">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ33">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN33)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN33)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA33">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO33)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP33)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO33)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP33)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB33">
-        <f>IF(BQ33='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ33='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC33">
-        <f>IF(BS33='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS33='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD33">
-        <f>IFERROR(VLOOKUP(BT33,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT33,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE33">
-        <f>IF(BR33='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR33='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF33" s="7">
@@ -16180,35 +15809,35 @@
         <v>9.5</v>
       </c>
       <c r="BX34">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY34">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ34">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN34)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN34)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA34">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO34)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP34)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO34)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP34)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB34">
-        <f>IF(BQ34='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ34='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC34">
-        <f>IF(BS34='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS34='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD34">
-        <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE34">
-        <f>IF(BR34='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR34='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF34" s="7">
@@ -16443,35 +16072,35 @@
         <v>14.5</v>
       </c>
       <c r="BX35">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY35">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ35">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN35)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN35)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA35">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO35)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP35)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO35)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP35)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB35">
-        <f>IF(BQ35='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ35='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC35">
-        <f>IF(BS35='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS35='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD35">
-        <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE35">
-        <f>IF(BR35='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR35='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF35" s="7">
@@ -16706,35 +16335,35 @@
         <v>14.5</v>
       </c>
       <c r="BX36">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY36">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ36">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN36)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN36)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA36">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO36)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP36)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO36)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP36)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB36">
-        <f>IF(BQ36='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ36='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC36">
-        <f>IF(BS36='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS36='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD36">
-        <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE36">
-        <f>IF(BR36='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR36='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF36" s="7">
@@ -16969,35 +16598,35 @@
         <v>10.5</v>
       </c>
       <c r="BX37">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY37">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ37">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN37)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN37)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA37">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO37)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP37)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO37)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP37)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB37">
-        <f>IF(BQ37='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ37='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC37">
-        <f>IF(BS37='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS37='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD37">
-        <f>IFERROR(VLOOKUP(BT37,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT37,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE37">
-        <f>IF(BR37='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR37='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF37" s="7">
@@ -17235,35 +16864,35 @@
         <v>13.5</v>
       </c>
       <c r="BX38">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY38">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ38">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN38)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN38)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA38">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO38)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP38)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO38)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP38)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB38">
-        <f>IF(BQ38='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ38='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC38">
-        <f>IF(BS38='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS38='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD38">
-        <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE38">
-        <f>IF(BR38='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR38='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF38" s="7">
@@ -17501,35 +17130,35 @@
         <v>11.5</v>
       </c>
       <c r="BX39">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY39">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ39">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN39)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN39)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA39">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO39)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP39)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO39)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP39)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB39">
-        <f>IF(BQ39='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ39='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC39">
-        <f>IF(BS39='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS39='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD39">
-        <f>IFERROR(VLOOKUP(BT39,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT39,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE39">
-        <f>IF(BR39='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR39='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF39" s="7">
@@ -17767,35 +17396,35 @@
         <v>12</v>
       </c>
       <c r="BX40">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY40">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ40">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN40)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN40)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA40">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO40)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP40)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO40)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP40)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB40">
-        <f>IF(BQ40='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ40='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC40">
-        <f>IF(BS40='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS40='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD40">
-        <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE40">
-        <f>IF(BR40='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR40='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF40" s="7">
@@ -18030,35 +17659,35 @@
         <v>8.5</v>
       </c>
       <c r="BX41">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY41">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ41">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN41)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN41)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA41">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO41)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP41)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO41)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP41)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB41">
-        <f>IF(BQ41='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ41='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC41">
-        <f>IF(BS41='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS41='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD41">
-        <f>IFERROR(VLOOKUP(BT41,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT41,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE41">
-        <f>IF(BR41='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR41='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF41" s="7">
@@ -18293,35 +17922,35 @@
         <v>10.5</v>
       </c>
       <c r="BX42">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY42">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ42">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN42)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN42)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA42">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO42)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP42)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO42)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP42)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB42">
-        <f>IF(BQ42='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ42='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC42">
-        <f>IF(BS42='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS42='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD42">
-        <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE42">
-        <f>IF(BR42='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR42='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF42" s="7">
@@ -18559,35 +18188,35 @@
         <v>12.5</v>
       </c>
       <c r="BX43">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY43">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ43">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN43)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN43)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA43">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO43)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP43)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO43)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP43)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB43">
-        <f>IF(BQ43='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ43='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC43">
-        <f>IF(BS43='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS43='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD43">
-        <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE43">
-        <f>IF(BR43='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR43='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF43" s="7">
@@ -18822,35 +18451,35 @@
         <v>13</v>
       </c>
       <c r="BX44">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY44">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ44">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN44)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN44)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA44">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO44)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP44)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO44)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP44)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB44">
-        <f>IF(BQ44='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ44='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC44">
-        <f>IF(BS44='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS44='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD44">
-        <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE44">
-        <f>IF(BR44='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR44='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF44" s="7">
@@ -19085,35 +18714,35 @@
         <v>14.5</v>
       </c>
       <c r="BX45">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY45">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ45">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN45)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN45)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA45">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO45)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP45)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO45)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP45)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB45">
-        <f>IF(BQ45='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ45='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC45">
-        <f>IF(BS45='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS45='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD45">
-        <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE45">
-        <f>IF(BR45='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR45='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF45" s="7">
@@ -19351,35 +18980,35 @@
         <v>14</v>
       </c>
       <c r="BX46">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY46">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ46">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN46)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN46)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA46">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO46)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP46)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO46)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP46)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB46">
-        <f>IF(BQ46='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ46='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC46">
-        <f>IF(BS46='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS46='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD46">
-        <f>IFERROR(VLOOKUP(BT46,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT46,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE46">
-        <f>IF(BR46='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR46='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF46" s="7">
@@ -19614,35 +19243,35 @@
         <v>13</v>
       </c>
       <c r="BX47">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY47">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ47">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN47)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN47)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA47">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO47)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP47)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO47)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP47)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB47">
-        <f>IF(BQ47='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ47='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC47">
-        <f>IF(BS47='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS47='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD47">
-        <f>IFERROR(VLOOKUP(BT47,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT47,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE47">
-        <f>IF(BR47='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR47='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF47" s="7">
@@ -19877,35 +19506,35 @@
         <v>11.5</v>
       </c>
       <c r="BX48">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY48">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ48">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN48)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN48)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA48">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO48)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP48)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO48)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP48)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB48">
-        <f>IF(BQ48='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ48='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC48">
-        <f>IF(BS48='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS48='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD48">
-        <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>2</v>
       </c>
       <c r="CE48">
-        <f>IF(BR48='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR48='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF48" s="7">
@@ -20143,35 +19772,35 @@
         <v>8</v>
       </c>
       <c r="BX49">
-        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$17,BB49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BY49">
-        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BC49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BD49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BE49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BF49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BG49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BH49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BI49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$9,BJ49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BC49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BD49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BE49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BF49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BG49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BH49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BI49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$G$2:$G$9,BJ49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BZ49">
-        <f>IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BK49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BL49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$K$2:$K$5,BN49)&gt;0,1,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BK49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BL49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$H$2:$H$5,BN49)&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CA49">
-        <f>IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BO49)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$M$2:$M$3,BP49)&gt;0,3,0)</f>
+        <f>IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BO49)&gt;0,3,0)+IF(COUNTIF('Resultats Reals'!$I$2:$I$3,BP49)&gt;0,3,0)</f>
         <v>0</v>
       </c>
       <c r="CB49">
-        <f>IF(BQ49='Resultats Reals'!$N$2,5,0)</f>
+        <f>IF(BQ49='Resultats Reals'!$J$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CC49">
-        <f>IF(BS49='Resultats Reals'!$O$2,5,0)</f>
+        <f>IF(BS49='Resultats Reals'!$K$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CD49">
-        <f>IFERROR(VLOOKUP(BT49,'Resultats Reals'!$R$2:$S$100,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(BT49,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="CE49">
-        <f>IF(BR49='Resultats Reals'!$P$2,5,0)</f>
+        <f>IF(BR49='Resultats Reals'!$L$2,5,0)</f>
         <v>0</v>
       </c>
       <c r="CF49" s="7">
@@ -20601,243 +20230,526 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>90</v>
       </c>
+      <c r="B1" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>248</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>119</v>
       </c>
+      <c r="B2" s="2" t="str" cm="1">
+        <f t="array" ref="B2">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C2,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C2" s="2" t="str" cm="1">
+        <f t="array" ref="C2">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E2,'Resultats Reals'!C2:C37))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
+      <c r="B3" s="2" t="str" cm="1">
+        <f t="array" ref="B3">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C3" s="2" t="str" cm="1">
+        <f t="array" ref="C3">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E3,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>117</v>
       </c>
+      <c r="B4" s="2" t="str" cm="1">
+        <f t="array" ref="B4">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C4" s="2" t="str" cm="1">
+        <f t="array" ref="C4">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E4,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>95</v>
       </c>
+      <c r="B5" s="2" t="str" cm="1">
+        <f t="array" ref="B5">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C5" s="2" t="str" cm="1">
+        <f t="array" ref="C5">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E5,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>127</v>
       </c>
+      <c r="B6" s="2" t="str" cm="1">
+        <f t="array" ref="B6">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C6" s="2" t="str" cm="1">
+        <f t="array" ref="C6">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E6,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
+      <c r="B7" s="2" t="str" cm="1">
+        <f t="array" ref="B7">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C7" s="2" t="str" cm="1">
+        <f t="array" ref="C7">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E7,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
+      <c r="B8" s="2" t="str" cm="1">
+        <f t="array" ref="B8">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C8" s="2" t="str" cm="1">
+        <f t="array" ref="C8">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E8,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>246</v>
       </c>
+      <c r="B9" s="2" t="str" cm="1">
+        <f t="array" ref="B9">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C9" s="2" t="str" cm="1">
+        <f t="array" ref="C9">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E9,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
+      <c r="B10" s="2" t="str" cm="1">
+        <f t="array" ref="B10">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C10" s="2" t="str" cm="1">
+        <f t="array" ref="C10">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E10,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
+      <c r="B11" s="2" t="str" cm="1">
+        <f t="array" ref="B11">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C11" s="2" t="str" cm="1">
+        <f t="array" ref="C11">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E11,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>143</v>
       </c>
+      <c r="B12" s="2" t="str" cm="1">
+        <f t="array" ref="B12">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C12" s="2" t="str" cm="1">
+        <f t="array" ref="C12">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E12,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>108</v>
       </c>
+      <c r="B13" s="2" t="str" cm="1">
+        <f t="array" ref="B13">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C13" s="2" t="str" cm="1">
+        <f t="array" ref="C13">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E13,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
+      <c r="B14" s="2" t="str" cm="1">
+        <f t="array" ref="B14">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C14" s="2" t="str" cm="1">
+        <f t="array" ref="C14">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E14,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
+      <c r="B15" s="2" t="str" cm="1">
+        <f t="array" ref="B15">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C15" s="2" t="str" cm="1">
+        <f t="array" ref="C15">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E15,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
+      <c r="B16" s="2" t="str" cm="1">
+        <f t="array" ref="B16">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C16" s="2" t="str" cm="1">
+        <f t="array" ref="C16">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E16,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>142</v>
       </c>
+      <c r="B17" s="2" t="str" cm="1">
+        <f t="array" ref="B17">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C17" s="2" t="str" cm="1">
+        <f t="array" ref="C17">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E17,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>104</v>
       </c>
+      <c r="B18" s="2" t="str" cm="1">
+        <f t="array" ref="B18">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C18" s="2" t="str" cm="1">
+        <f t="array" ref="C18">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E18,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
+      <c r="B19" s="2" t="str" cm="1">
+        <f t="array" ref="B19">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C19" s="2" t="str" cm="1">
+        <f t="array" ref="C19">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E19,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>112</v>
       </c>
+      <c r="B20" s="2" t="str" cm="1">
+        <f t="array" ref="B20">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C20" s="2" t="str" cm="1">
+        <f t="array" ref="C20">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E20,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
+      <c r="B21" s="2" t="str" cm="1">
+        <f t="array" ref="B21">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C21" s="2" t="str" cm="1">
+        <f t="array" ref="C21">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E21,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>89</v>
       </c>
+      <c r="B22" s="2" t="str" cm="1">
+        <f t="array" ref="B22">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C22" s="2" t="str" cm="1">
+        <f t="array" ref="C22">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E22,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
+      <c r="B23" s="2" t="str" cm="1">
+        <f t="array" ref="B23">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C23" s="2" t="str" cm="1">
+        <f t="array" ref="C23">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E23,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
+      <c r="B24" s="2" t="str" cm="1">
+        <f t="array" ref="B24">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C24" s="2" t="str" cm="1">
+        <f t="array" ref="C24">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E24,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>171</v>
       </c>
+      <c r="B25" s="2" t="str" cm="1">
+        <f t="array" ref="B25">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C25" s="2" t="str" cm="1">
+        <f t="array" ref="C25">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E25,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
+      <c r="B26" s="2" t="str" cm="1">
+        <f t="array" ref="B26">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C26" s="2" t="str" cm="1">
+        <f t="array" ref="C26">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E26,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
+      <c r="B27" s="2" t="str" cm="1">
+        <f t="array" ref="B27">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C27" s="2" t="str" cm="1">
+        <f t="array" ref="C27">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E27,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>144</v>
       </c>
+      <c r="B28" s="2" t="str" cm="1">
+        <f t="array" ref="B28">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C28" s="2" t="str" cm="1">
+        <f t="array" ref="C28">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E28,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>100</v>
       </c>
+      <c r="B29" s="2" t="str" cm="1">
+        <f t="array" ref="B29">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C29" s="2" t="str" cm="1">
+        <f t="array" ref="C29">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E29,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
+      <c r="B30" s="2" t="str" cm="1">
+        <f t="array" ref="B30">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C30" s="2" t="str" cm="1">
+        <f t="array" ref="C30">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E30,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>118</v>
       </c>
+      <c r="B31" s="2" t="str" cm="1">
+        <f t="array" ref="B31">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C31" s="2" t="str" cm="1">
+        <f t="array" ref="C31">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E31,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>139</v>
       </c>
+      <c r="B32" s="2" t="str" cm="1">
+        <f t="array" ref="B32">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C32" s="2" t="str" cm="1">
+        <f t="array" ref="C32">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E32,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>145</v>
       </c>
+      <c r="B33" s="2" t="str" cm="1">
+        <f t="array" ref="B33">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C33" s="2" t="str" cm="1">
+        <f t="array" ref="C33">IF(SUMPRODUCT(--EXACT('Resultats Reals'!E33,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>91</v>
       </c>
+      <c r="B34" s="2" t="str" cm="1">
+        <f t="array" ref="B34">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C34,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>113</v>
       </c>
+      <c r="B35" s="2" t="str" cm="1">
+        <f t="array" ref="B35">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C35,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>96</v>
       </c>
+      <c r="B36" s="2" t="str" cm="1">
+        <f t="array" ref="B36">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C36,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>126</v>
       </c>
+      <c r="B37" s="2" t="str" cm="1">
+        <f t="array" ref="B37">IF(SUMPRODUCT(--EXACT('Resultats Reals'!C37,Països_ok!$A$1:$A$47))&gt;0,"OK","Revisar")</f>
+        <v>OK</v>
+      </c>
+      <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>120</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB7B02F-D8FD-42C3-A0F7-CEB028CB1E06}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8993165-A050-465E-AB04-EA8CBA683006}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3804" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="249">
   <si>
     <t>Participants</t>
   </si>
@@ -846,7 +846,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,6 +893,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -936,7 +942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -961,6 +967,9 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,7 +988,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marc Llopis" refreshedDate="46191.502336689817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marc Llopis" refreshedDate="46196.49204571759" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CF49" sheet="Porra"/>
   </cacheSource>
@@ -1256,13 +1265,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Punts Grups 1r" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="13" maxValue="19"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16" maxValue="22"/>
     </cacheField>
     <cacheField name="Punts Grups 2n" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8" maxValue="16"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="11" maxValue="18"/>
     </cacheField>
     <cacheField name="Punts Grups 3r" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.5" maxValue="12.5"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.5" maxValue="15.5"/>
     </cacheField>
     <cacheField name="Punts Vuitens" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
@@ -1283,13 +1292,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Punts Pichichi" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
     </cacheField>
     <cacheField name="Resultat Final2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Total Punts" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="28.5" maxValue="45.5"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="38.5" maxValue="56"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1375,18 +1384,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="18"/>
-    <n v="12"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="39"/>
+    <n v="21"/>
+    <n v="13"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="47.5"/>
   </r>
   <r>
     <x v="1"/>
@@ -1461,18 +1470,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="18"/>
-    <n v="15"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="45.5"/>
+    <n v="21"/>
+    <n v="16"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="52"/>
   </r>
   <r>
     <x v="2"/>
@@ -1547,18 +1556,18 @@
     <m/>
     <s v="Rodri"/>
     <s v="Nico Williams"/>
-    <n v="18"/>
-    <n v="13"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="40"/>
+    <n v="21"/>
+    <n v="14"/>
+    <n v="7.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="3"/>
@@ -1633,18 +1642,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="14"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="45.5"/>
+    <n v="22"/>
+    <n v="18"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="56"/>
   </r>
   <r>
     <x v="4"/>
@@ -1719,18 +1728,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="41.5"/>
+    <n v="19"/>
+    <n v="15"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="49.5"/>
   </r>
   <r>
     <x v="5"/>
@@ -1805,18 +1814,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="44.5"/>
+    <n v="21"/>
+    <n v="15"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="51"/>
   </r>
   <r>
     <x v="6"/>
@@ -1891,18 +1900,18 @@
     <m/>
     <s v="Julián Álvarez"/>
     <s v="Julián Álvarez"/>
-    <n v="14"/>
-    <n v="11"/>
-    <n v="3.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="28.5"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="6.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="38.5"/>
   </r>
   <r>
     <x v="7"/>
@@ -1977,18 +1986,18 @@
     <s v="1-3"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="15"/>
-    <n v="13"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="17"/>
+    <n v="14"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="47.5"/>
   </r>
   <r>
     <x v="8"/>
@@ -2063,18 +2072,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Kylian Mbappé"/>
-    <n v="15"/>
-    <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="40.5"/>
+    <n v="20"/>
+    <n v="16"/>
+    <n v="14"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="54"/>
   </r>
   <r>
     <x v="9"/>
@@ -2149,18 +2158,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="15"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="42"/>
+    <n v="19"/>
+    <n v="17"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="48"/>
   </r>
   <r>
     <x v="10"/>
@@ -2235,18 +2244,18 @@
     <m/>
     <s v="Julián Álvarez"/>
     <s v="Kylian Mbappé"/>
-    <n v="13"/>
+    <n v="16"/>
+    <n v="15"/>
     <n v="11"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="36.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="46"/>
   </r>
   <r>
     <x v="11"/>
@@ -2321,18 +2330,18 @@
     <m/>
     <s v="Harry Kane"/>
     <s v="Kylian Mbappé"/>
-    <n v="13"/>
-    <n v="12"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="19"/>
+    <n v="15"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="48.5"/>
   </r>
   <r>
     <x v="12"/>
@@ -2407,18 +2416,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Lamine Yamal"/>
-    <n v="18"/>
-    <n v="12"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="21"/>
+    <n v="13"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="46.5"/>
   </r>
   <r>
     <x v="13"/>
@@ -2493,18 +2502,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Julián Álvarez"/>
+    <n v="20"/>
     <n v="17"/>
-    <n v="15"/>
-    <n v="7.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="49.5"/>
   </r>
   <r>
     <x v="14"/>
@@ -2579,18 +2588,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Julián Álvarez"/>
-    <n v="19"/>
-    <n v="13"/>
-    <n v="7.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="22"/>
+    <n v="15"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="47.5"/>
   </r>
   <r>
     <x v="15"/>
@@ -2665,18 +2674,18 @@
     <m/>
     <s v="Raphinha"/>
     <s v="Erling Haaland"/>
-    <n v="16"/>
-    <n v="8"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="38.5"/>
+    <n v="20"/>
+    <n v="11"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="45.5"/>
   </r>
   <r>
     <x v="16"/>
@@ -2751,18 +2760,18 @@
     <s v="2-0"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="12"/>
-    <n v="7.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="37.5"/>
+    <n v="19"/>
+    <n v="13"/>
+    <n v="8.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="44.5"/>
   </r>
   <r>
     <x v="17"/>
@@ -2837,18 +2846,18 @@
     <m/>
     <s v="Vinícius Júnior"/>
     <s v="Vinícius Júnior"/>
-    <n v="17"/>
+    <n v="20"/>
     <n v="13"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="46.5"/>
   </r>
   <r>
     <x v="18"/>
@@ -2923,18 +2932,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
+    <n v="19"/>
+    <n v="12"/>
     <n v="11"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="39"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="46"/>
   </r>
   <r>
     <x v="19"/>
@@ -3009,18 +3018,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="11"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="19"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="50"/>
   </r>
   <r>
     <x v="20"/>
@@ -3095,18 +3104,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
+    <n v="19"/>
     <n v="13"/>
-    <n v="11"/>
-    <n v="8.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="34.5"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="46.5"/>
   </r>
   <r>
     <x v="21"/>
@@ -3181,9 +3190,9 @@
     <m/>
     <s v="Erling Haaland"/>
     <s v="Harry Kane"/>
+    <n v="19"/>
     <n v="13"/>
-    <n v="11"/>
-    <n v="8.5"/>
+    <n v="10.5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3192,7 +3201,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="34.5"/>
+    <n v="44.5"/>
   </r>
   <r>
     <x v="22"/>
@@ -3267,18 +3276,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Kylian Mbappé"/>
-    <n v="18"/>
-    <n v="16"/>
-    <n v="6.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="21"/>
+    <n v="17"/>
+    <n v="14"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="56"/>
   </r>
   <r>
     <x v="23"/>
@@ -3353,18 +3362,18 @@
     <m/>
     <s v="Kylian Mbappé"/>
     <s v="Rodri"/>
+    <n v="19"/>
     <n v="13"/>
-    <n v="11"/>
-    <n v="8.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="32.5"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="24"/>
@@ -3439,18 +3448,18 @@
     <s v="2026-01-02"/>
     <s v="Kylian Mbappé"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="13"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="48"/>
   </r>
   <r>
     <x v="25"/>
@@ -3525,18 +3534,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
+    <n v="18"/>
     <n v="15"/>
-    <n v="11"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="36.5"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="47"/>
   </r>
   <r>
     <x v="26"/>
@@ -3611,18 +3620,18 @@
     <m/>
     <s v="Doué"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="41.5"/>
+    <n v="18"/>
+    <n v="14"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="47"/>
   </r>
   <r>
     <x v="27"/>
@@ -3697,18 +3706,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="10"/>
-    <n v="9.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="38.5"/>
+    <n v="22"/>
+    <n v="11"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="48"/>
   </r>
   <r>
     <x v="28"/>
@@ -3783,18 +3792,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="36"/>
+    <n v="18"/>
+    <n v="13"/>
+    <n v="9.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="29"/>
@@ -3869,18 +3878,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="9.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="38.5"/>
+    <n v="20"/>
+    <n v="14"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="50.5"/>
   </r>
   <r>
     <x v="30"/>
@@ -3955,18 +3964,18 @@
     <s v="2026-02-01"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="14"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="42"/>
+    <n v="22"/>
+    <n v="16"/>
+    <n v="9.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="51.5"/>
   </r>
   <r>
     <x v="31"/>
@@ -4041,18 +4050,18 @@
     <s v="2026-01-03"/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="16"/>
-    <n v="11"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="37.5"/>
+    <n v="19"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="48"/>
   </r>
   <r>
     <x v="32"/>
@@ -4127,18 +4136,18 @@
     <s v="2026-02-03"/>
     <s v="Harry Kane"/>
     <s v="Kylian Mbappé"/>
-    <n v="18"/>
-    <n v="14"/>
-    <n v="8.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="21"/>
+    <n v="16"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="50"/>
   </r>
   <r>
     <x v="33"/>
@@ -4213,9 +4222,9 @@
     <m/>
     <s v="Vinícius Júnior"/>
     <s v="Harry Kane"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="12"/>
+    <n v="18"/>
+    <n v="14"/>
+    <n v="15.5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4224,7 +4233,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="41"/>
+    <n v="49.5"/>
   </r>
   <r>
     <x v="34"/>
@@ -4299,9 +4308,9 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Harry Kane"/>
-    <n v="16"/>
-    <n v="12"/>
-    <n v="12"/>
+    <n v="18"/>
+    <n v="13"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4310,7 +4319,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="42"/>
+    <n v="48"/>
   </r>
   <r>
     <x v="35"/>
@@ -4385,18 +4394,18 @@
     <m/>
     <s v="Vitinha"/>
     <s v="Endrick"/>
-    <n v="17"/>
+    <n v="18"/>
     <n v="15"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="43"/>
   </r>
   <r>
     <x v="36"/>
@@ -4471,18 +4480,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="12"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="40.5"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="49.5"/>
   </r>
   <r>
     <x v="37"/>
@@ -4557,18 +4566,18 @@
     <s v="2026-02-02"/>
     <s v="Pedri"/>
     <s v="Sørloth"/>
-    <n v="17"/>
-    <n v="12"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="18"/>
+    <n v="13"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="42"/>
   </r>
   <r>
     <x v="38"/>
@@ -4643,18 +4652,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="17"/>
+    <n v="13"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="45.5"/>
   </r>
   <r>
     <x v="39"/>
@@ -4729,18 +4738,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Julián Álvarez"/>
-    <n v="18"/>
-    <n v="12"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="39"/>
+    <n v="21"/>
+    <n v="16"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="45"/>
   </r>
   <r>
     <x v="40"/>
@@ -4815,18 +4824,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
+    <n v="22"/>
     <n v="17"/>
-    <n v="15"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="45"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="54.5"/>
   </r>
   <r>
     <x v="41"/>
@@ -4901,9 +4910,9 @@
     <s v="2026-01-03"/>
     <s v="Lamine Yamal"/>
     <s v="Harry Kane"/>
-    <n v="16"/>
-    <n v="13"/>
-    <n v="12"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="13.5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4912,7 +4921,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="43"/>
+    <n v="48.5"/>
   </r>
   <r>
     <x v="42"/>
@@ -4987,18 +4996,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="14"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="44.5"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="14.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="53.5"/>
   </r>
   <r>
     <x v="43"/>
@@ -5073,9 +5082,9 @@
     <m/>
     <s v="Kylian Mbappé"/>
     <s v="Harry Kane"/>
-    <n v="17"/>
-    <n v="12"/>
-    <n v="7.5"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="14"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5084,7 +5093,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="38.5"/>
+    <n v="49"/>
   </r>
   <r>
     <x v="44"/>
@@ -5159,18 +5168,18 @@
     <s v="2026-04-03"/>
     <s v="Lamine Yamal"/>
     <s v="Ferran Torres"/>
-    <n v="18"/>
-    <n v="14"/>
-    <n v="8.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="40.5"/>
+    <n v="21"/>
+    <n v="16"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="52"/>
   </r>
   <r>
     <x v="45"/>
@@ -5245,18 +5254,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Lamine Yamal"/>
-    <n v="14"/>
-    <n v="10"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="34.5"/>
+    <n v="18"/>
+    <n v="11"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="46"/>
@@ -5331,18 +5340,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="15"/>
-    <n v="6.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="39.5"/>
+    <n v="21"/>
+    <n v="18"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="53.5"/>
   </r>
   <r>
     <x v="47"/>
@@ -5417,24 +5426,24 @@
     <s v="3-1"/>
     <s v="Kylian Mbappé"/>
     <s v="Lamine Yamal"/>
-    <n v="15"/>
-    <n v="13"/>
-    <n v="9.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="37.5"/>
+    <n v="21"/>
+    <n v="16"/>
+    <n v="7.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="44.5"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -5594,7 +5603,7 @@
   </rowFields>
   <rowItems count="49">
     <i>
-      <x v="47"/>
+      <x v="35"/>
     </i>
     <i>
       <x v="26"/>
@@ -5603,25 +5612,64 @@
       <x v="7"/>
     </i>
     <i>
-      <x v="39"/>
+      <x v="10"/>
     </i>
     <i>
       <x v="24"/>
     </i>
     <i>
-      <x v="31"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="35"/>
+      <x v="6"/>
     </i>
     <i>
-      <x v="19"/>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="14"/>
     </i>
     <i>
       <x v="30"/>
     </i>
     <i>
-      <x v="16"/>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="40"/>
     </i>
     <i>
       <x v="33"/>
@@ -5630,82 +5678,43 @@
       <x v="27"/>
     </i>
     <i>
-      <x v="45"/>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="8"/>
     </i>
     <i>
       <x v="34"/>
     </i>
     <i>
-      <x v="8"/>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="32"/>
     </i>
     <i>
       <x v="21"/>
     </i>
     <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
       <x v="42"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="38"/>
     </i>
     <i>
       <x v="13"/>
@@ -5714,25 +5723,25 @@
       <x v="50"/>
     </i>
     <i>
-      <x v="20"/>
+      <x v="51"/>
     </i>
     <i>
-      <x v="22"/>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="52"/>
     </i>
     <i>
       <x v="37"/>
     </i>
     <i>
-      <x v="18"/>
+      <x v="25"/>
     </i>
     <i>
-      <x v="15"/>
+      <x v="17"/>
     </i>
     <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
+      <x v="18"/>
     </i>
     <i>
       <x v="3"/>
@@ -6111,8 +6120,9 @@
       <c r="C2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>90</v>
+      <c r="E2" s="14" t="str">
+        <f>+C2</f>
+        <v>Mèxic</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>229</v>
@@ -6139,7 +6149,7 @@
         <v>158</v>
       </c>
       <c r="O2" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -6152,8 +6162,9 @@
       <c r="C3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>97</v>
+      <c r="E3" s="14" t="str">
+        <f>+C3</f>
+        <v>Corea del Sud</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>229</v>
@@ -6171,7 +6182,7 @@
         <v>162</v>
       </c>
       <c r="O3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -6181,11 +6192,12 @@
       <c r="B4" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>95</v>
+      <c r="E4" s="14" t="str">
+        <f>+C5</f>
+        <v>Canadà</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>229</v>
@@ -6197,10 +6209,10 @@
         <v>229</v>
       </c>
       <c r="N4" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="O4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -6213,8 +6225,9 @@
       <c r="C5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>127</v>
+      <c r="E5" s="14" t="str">
+        <f>+C6</f>
+        <v>Suïssa</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>229</v>
@@ -6226,7 +6239,7 @@
         <v>229</v>
       </c>
       <c r="N5" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="O5" s="3">
         <v>2</v>
@@ -6242,8 +6255,9 @@
       <c r="C6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>107</v>
+      <c r="E6" s="14" t="str">
+        <f>+C8</f>
+        <v>Brasil</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>229</v>
@@ -6265,11 +6279,12 @@
       <c r="B7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>92</v>
+      <c r="E7" s="14" t="str">
+        <f>+C9</f>
+        <v>Marroc</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>229</v>
@@ -6278,10 +6293,10 @@
         <v>229</v>
       </c>
       <c r="N7" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="O7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -6294,8 +6309,9 @@
       <c r="C8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>88</v>
+      <c r="E8" s="14" t="str">
+        <f>+C11</f>
+        <v>Estats Units</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>229</v>
@@ -6304,7 +6320,7 @@
         <v>229</v>
       </c>
       <c r="N8" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -6320,8 +6336,9 @@
       <c r="C9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>99</v>
+      <c r="E9" s="14" t="str">
+        <f>+C12</f>
+        <v>Austràlia</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>229</v>
@@ -6330,7 +6347,7 @@
         <v>229</v>
       </c>
       <c r="N9" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -6343,17 +6360,18 @@
       <c r="B10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>143</v>
+      <c r="E10" s="14" t="str">
+        <f>+C14</f>
+        <v>Alemanya</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N10" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -6369,17 +6387,18 @@
       <c r="C11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>108</v>
+      <c r="E11" s="14" t="str">
+        <f>+C15</f>
+        <v>Costa d'Ivori</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -6392,8 +6411,9 @@
       <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>98</v>
+      <c r="E12" s="14" t="str">
+        <f>+C17</f>
+        <v>Països Baixos</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>229</v>
@@ -6412,11 +6432,12 @@
       <c r="B13" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>114</v>
+      <c r="E13" s="14" t="str">
+        <f>+C18</f>
+        <v>Japó</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>229</v>
@@ -6438,8 +6459,9 @@
       <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>109</v>
+      <c r="E14" s="14" t="str">
+        <f>+C20</f>
+        <v>Egipte</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>229</v>
@@ -6461,8 +6483,9 @@
       <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>104</v>
+      <c r="E15" s="14" t="str">
+        <f>+C21</f>
+        <v>Iran</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>229</v>
@@ -6475,11 +6498,12 @@
       <c r="B16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>112</v>
+      <c r="E16" s="14" t="str">
+        <f>+C23</f>
+        <v>Espanya</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>229</v>
@@ -6495,8 +6519,9 @@
       <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>93</v>
+      <c r="E17" s="14" t="str">
+        <f>+C24</f>
+        <v>Uruguai</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>229</v>
@@ -6512,8 +6537,9 @@
       <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>89</v>
+      <c r="E18" s="14" t="str">
+        <f>+C26</f>
+        <v>França</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,11 +6549,12 @@
       <c r="B19" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>94</v>
+      <c r="E19" s="14" t="str">
+        <f>+C27</f>
+        <v>Noruega</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,8 +6567,9 @@
       <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>121</v>
+      <c r="E20" s="14" t="str">
+        <f>+C29</f>
+        <v>Argentina</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6554,8 +6582,9 @@
       <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>116</v>
+      <c r="E21" s="14" t="str">
+        <f>+C30</f>
+        <v>Àustria</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6565,11 +6594,12 @@
       <c r="B22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>115</v>
+      <c r="E22" s="14" t="str">
+        <f>+C32</f>
+        <v>Colòmbia</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,8 +6612,9 @@
       <c r="C23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>100</v>
+      <c r="E23" s="14" t="str">
+        <f>+C33</f>
+        <v>RD Congo</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6596,8 +6627,9 @@
       <c r="C24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>86</v>
+      <c r="E24" s="14" t="str">
+        <f>+C35</f>
+        <v>Anglaterra</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6607,11 +6639,12 @@
       <c r="B25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>118</v>
+      <c r="E25" s="14" t="str">
+        <f>+C36</f>
+        <v>Ghana</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6622,10 +6655,10 @@
         <v>228</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -6637,10 +6670,10 @@
         <v>230</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6650,11 +6683,11 @@
       <c r="B28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="16" t="s">
         <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -6668,7 +6701,7 @@
         <v>95</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6682,7 +6715,7 @@
         <v>107</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -6692,11 +6725,11 @@
       <c r="B31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>144</v>
+      <c r="C31" s="17" t="s">
+        <v>119</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -6724,7 +6757,7 @@
         <v>128</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6734,7 +6767,7 @@
       <c r="B34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="16" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6757,7 +6790,7 @@
         <v>230</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6767,8 +6800,8 @@
       <c r="B37" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>121</v>
+      <c r="C37" s="16" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -7361,15 +7394,15 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7405,7 +7438,7 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.25">
@@ -7624,7 +7657,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
@@ -7632,7 +7665,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7660,7 +7693,7 @@
       </c>
       <c r="CD3">
         <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE3">
         <f>IF(BR3='Resultats Reals'!$L$2,5,0)</f>
@@ -7668,7 +7701,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.25">
@@ -7887,15 +7920,15 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7931,7 +7964,7 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.25">
@@ -8150,15 +8183,15 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8186,7 +8219,7 @@
       </c>
       <c r="CD5">
         <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE5">
         <f>IF(BR5='Resultats Reals'!$L$2,5,0)</f>
@@ -8194,7 +8227,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.25">
@@ -8413,7 +8446,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
@@ -8421,7 +8454,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8449,7 +8482,7 @@
       </c>
       <c r="CD6">
         <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE6">
         <f>IF(BR6='Resultats Reals'!$L$2,5,0)</f>
@@ -8457,7 +8490,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8676,7 +8709,7 @@
       </c>
       <c r="BU7">
         <f>IF(C7='Resultats Reals'!$C$2,2,IF(OR(C7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C7)&gt;0),1,0))+IF(D7='Resultats Reals'!$C$5,2,IF(OR(D7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D7)&gt;0),1,0))+IF(E7='Resultats Reals'!$C$8,2,IF(OR(E7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E7)&gt;0),1,0))+IF(F7='Resultats Reals'!$C$11,2,IF(OR(F7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F7)&gt;0),1,0))+IF(G7='Resultats Reals'!$C$14,2,IF(OR(G7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G7)&gt;0),1,0))+IF(H7='Resultats Reals'!$C$17,2,IF(OR(H7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H7)&gt;0),1,0))+IF(I7='Resultats Reals'!$C$20,2,IF(OR(I7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I7)&gt;0),1,0))+IF(J7='Resultats Reals'!$C$23,2,IF(OR(J7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J7)&gt;0),1,0))+IF(K7='Resultats Reals'!$C$26,2,IF(OR(K7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K7)&gt;0),1,0))+IF(L7='Resultats Reals'!$C$29,2,IF(OR(L7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L7)&gt;0),1,0))+IF(M7='Resultats Reals'!$C$32,2,IF(OR(M7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M7)&gt;0),1,0))+IF(N7='Resultats Reals'!$C$35,2,IF(OR(N7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N7)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z7)&gt;0),1,0))</f>
@@ -8684,7 +8717,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8712,7 +8745,7 @@
       </c>
       <c r="CD7">
         <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE7">
         <f>IF(BR7='Resultats Reals'!$L$2,5,0)</f>
@@ -8720,7 +8753,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.25">
@@ -8943,7 +8976,7 @@
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
@@ -8983,7 +9016,7 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.25">
@@ -9205,15 +9238,15 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N9)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z9)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9241,7 +9274,7 @@
       </c>
       <c r="CD9">
         <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE9">
         <f>IF(BR9='Resultats Reals'!$L$2,5,0)</f>
@@ -9249,7 +9282,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.25">
@@ -9468,15 +9501,15 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
@@ -9504,7 +9537,7 @@
       </c>
       <c r="CD10">
         <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE10">
         <f>IF(BR10='Resultats Reals'!$L$2,5,0)</f>
@@ -9512,7 +9545,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
@@ -9731,7 +9764,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
@@ -9767,7 +9800,7 @@
       </c>
       <c r="CD11">
         <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE11">
         <f>IF(BR11='Resultats Reals'!$L$2,5,0)</f>
@@ -9775,7 +9808,7 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
@@ -9998,11 +10031,11 @@
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
@@ -10030,7 +10063,7 @@
       </c>
       <c r="CD12">
         <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE12">
         <f>IF(BR12='Resultats Reals'!$L$2,5,0)</f>
@@ -10038,7 +10071,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.25">
@@ -10257,15 +10290,15 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10293,7 +10326,7 @@
       </c>
       <c r="CD13">
         <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE13">
         <f>IF(BR13='Resultats Reals'!$L$2,5,0)</f>
@@ -10301,7 +10334,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.25">
@@ -10520,15 +10553,15 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
@@ -10564,7 +10597,7 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.25">
@@ -10783,7 +10816,7 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
@@ -10791,7 +10824,7 @@
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
@@ -10827,7 +10860,7 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.25">
@@ -11046,7 +11079,7 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
@@ -11054,7 +11087,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11090,7 +11123,7 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.25">
@@ -11309,15 +11342,15 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N17)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX17">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
@@ -11345,7 +11378,7 @@
       </c>
       <c r="CD17">
         <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE17">
         <f>IF(BR17='Resultats Reals'!$L$2,5,0)</f>
@@ -11353,7 +11386,7 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.25">
@@ -11575,11 +11608,11 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
@@ -11611,7 +11644,7 @@
       </c>
       <c r="CD18">
         <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE18">
         <f>IF(BR18='Resultats Reals'!$L$2,5,0)</f>
@@ -11619,7 +11652,7 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
@@ -11838,15 +11871,15 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -12101,15 +12134,15 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12137,7 +12170,7 @@
       </c>
       <c r="CD20">
         <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE20">
         <f>IF(BR20='Resultats Reals'!$L$2,5,0)</f>
@@ -12145,7 +12178,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
@@ -12364,7 +12397,7 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
@@ -12372,7 +12405,7 @@
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
@@ -12400,7 +12433,7 @@
       </c>
       <c r="CD21">
         <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE21">
         <f>IF(BR21='Resultats Reals'!$L$2,5,0)</f>
@@ -12408,7 +12441,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.25">
@@ -12631,11 +12664,11 @@
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX22">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB22)&gt;0,1,0)</f>
@@ -12663,7 +12696,7 @@
       </c>
       <c r="CD22">
         <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE22">
         <f>IF(BR22='Resultats Reals'!$L$2,5,0)</f>
@@ -12671,7 +12704,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.25">
@@ -12894,11 +12927,11 @@
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX23">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB23)&gt;0,1,0)</f>
@@ -12934,7 +12967,7 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.25">
@@ -13153,7 +13186,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
@@ -13161,7 +13194,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13189,7 +13222,7 @@
       </c>
       <c r="CD24">
         <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE24">
         <f>IF(BR24='Resultats Reals'!$L$2,5,0)</f>
@@ -13197,7 +13230,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>53.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
@@ -13420,11 +13453,11 @@
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX25">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB25)&gt;0,1,0)</f>
@@ -13460,7 +13493,7 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="26" spans="1:84" x14ac:dyDescent="0.25">
@@ -13682,7 +13715,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
@@ -13690,7 +13723,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13718,7 +13751,7 @@
       </c>
       <c r="CD26">
         <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE26">
         <f>IF(BR26='Resultats Reals'!$L$2,5,0)</f>
@@ -13726,7 +13759,7 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
@@ -13945,15 +13978,15 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
@@ -13989,7 +14022,7 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.25">
@@ -14208,7 +14241,7 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N28)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z28)&gt;0),1,0))</f>
@@ -14216,7 +14249,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14244,7 +14277,7 @@
       </c>
       <c r="CD28">
         <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE28">
         <f>IF(BR28='Resultats Reals'!$L$2,5,0)</f>
@@ -14252,7 +14285,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.25">
@@ -14474,15 +14507,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14510,7 +14543,7 @@
       </c>
       <c r="CD29">
         <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE29">
         <f>IF(BR29='Resultats Reals'!$L$2,5,0)</f>
@@ -14518,7 +14551,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.25">
@@ -14737,15 +14770,15 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14781,7 +14814,7 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.25">
@@ -15000,7 +15033,7 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
@@ -15008,7 +15041,7 @@
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX31">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
@@ -15036,7 +15069,7 @@
       </c>
       <c r="CD31">
         <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE31">
         <f>IF(BR31='Resultats Reals'!$L$2,5,0)</f>
@@ -15044,7 +15077,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
@@ -15266,15 +15299,15 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15302,7 +15335,7 @@
       </c>
       <c r="CD32">
         <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE32">
         <f>IF(BR32='Resultats Reals'!$L$2,5,0)</f>
@@ -15310,7 +15343,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
@@ -15532,7 +15565,7 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
@@ -15540,7 +15573,7 @@
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
@@ -15576,7 +15609,7 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.25">
@@ -15798,15 +15831,15 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15834,7 +15867,7 @@
       </c>
       <c r="CD34">
         <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE34">
         <f>IF(BR34='Resultats Reals'!$L$2,5,0)</f>
@@ -15842,7 +15875,7 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
@@ -16061,15 +16094,15 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
@@ -16324,15 +16357,15 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N36)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z36)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16368,7 +16401,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.25">
@@ -16587,15 +16620,15 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16631,7 +16664,7 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.25">
@@ -16853,7 +16886,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
@@ -16861,7 +16894,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16889,7 +16922,7 @@
       </c>
       <c r="CD38">
         <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE38">
         <f>IF(BR38='Resultats Reals'!$L$2,5,0)</f>
@@ -16897,7 +16930,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
@@ -17119,15 +17152,15 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N39)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
@@ -17163,7 +17196,7 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.25">
@@ -17389,11 +17422,11 @@
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z40)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17421,7 +17454,7 @@
       </c>
       <c r="CD40">
         <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE40">
         <f>IF(BR40='Resultats Reals'!$L$2,5,0)</f>
@@ -17429,7 +17462,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
@@ -17648,7 +17681,7 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N41)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
@@ -17656,7 +17689,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
@@ -17692,7 +17725,7 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.25">
@@ -17911,15 +17944,15 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N42)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z42)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17947,7 +17980,7 @@
       </c>
       <c r="CD42">
         <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE42">
         <f>IF(BR42='Resultats Reals'!$L$2,5,0)</f>
@@ -17955,7 +17988,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>52.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.25">
@@ -18177,15 +18210,15 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N43)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z43)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
@@ -18440,15 +18473,15 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N44)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z44)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18476,7 +18509,7 @@
       </c>
       <c r="CD44">
         <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE44">
         <f>IF(BR44='Resultats Reals'!$L$2,5,0)</f>
@@ -18484,7 +18517,7 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.25">
@@ -18703,7 +18736,7 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N45)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z45)&gt;0),1,0))</f>
@@ -18711,7 +18744,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18747,7 +18780,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.25">
@@ -18969,15 +19002,15 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N46)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z46)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -19013,7 +19046,7 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.25">
@@ -19232,15 +19265,15 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N47)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z47)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
@@ -19276,7 +19309,7 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.25">
@@ -19495,15 +19528,15 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N48)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z48)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19531,7 +19564,7 @@
       </c>
       <c r="CD48">
         <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CE48">
         <f>IF(BR48='Resultats Reals'!$L$2,5,0)</f>
@@ -19539,7 +19572,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.25">
@@ -19761,15 +19794,15 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N49)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z49)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19805,7 +19838,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -19832,394 +19865,394 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2">
-        <v>45.5</v>
+        <v>174</v>
+      </c>
+      <c r="B2" s="18">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B3">
-        <v>45.5</v>
+      <c r="B3" s="18">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B4">
-        <v>45</v>
+      <c r="B4" s="18">
+        <v>54.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5">
-        <v>44.5</v>
+        <v>150</v>
+      </c>
+      <c r="B5" s="18">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B6">
-        <v>44.5</v>
+      <c r="B6" s="18">
+        <v>53.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7">
-        <v>43</v>
+        <v>214</v>
+      </c>
+      <c r="B7" s="18">
+        <v>53.5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8">
-        <v>42.5</v>
+        <v>210</v>
+      </c>
+      <c r="B8" s="18">
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9">
-        <v>42.5</v>
+        <v>124</v>
+      </c>
+      <c r="B9" s="18">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10">
-        <v>42.5</v>
+        <v>185</v>
+      </c>
+      <c r="B10" s="18">
+        <v>51.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="B11" s="18">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12">
-        <v>42</v>
+        <v>184</v>
+      </c>
+      <c r="B12" s="18">
+        <v>50.5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B13">
-        <v>42</v>
+        <v>169</v>
+      </c>
+      <c r="B13" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14">
-        <v>41.5</v>
+        <v>189</v>
+      </c>
+      <c r="B14" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15">
-        <v>41.5</v>
+        <v>157</v>
+      </c>
+      <c r="B15" s="18">
+        <v>49.5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16">
-        <v>41</v>
+        <v>191</v>
+      </c>
+      <c r="B16" s="18">
+        <v>49.5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B17">
-        <v>41</v>
+        <v>196</v>
+      </c>
+      <c r="B17" s="18">
+        <v>49.5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18">
-        <v>41</v>
+        <v>137</v>
+      </c>
+      <c r="B18" s="18">
+        <v>49.5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19">
-        <v>41</v>
+        <v>209</v>
+      </c>
+      <c r="B19" s="18">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20">
-        <v>41</v>
+        <v>154</v>
+      </c>
+      <c r="B20" s="18">
+        <v>48.5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21">
-        <v>41</v>
+        <v>206</v>
+      </c>
+      <c r="B21" s="18">
+        <v>48.5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B22">
-        <v>40.5</v>
+        <v>176</v>
+      </c>
+      <c r="B22" s="18">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B23">
-        <v>40.5</v>
+        <v>187</v>
+      </c>
+      <c r="B23" s="18">
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24">
-        <v>40.5</v>
+        <v>181</v>
+      </c>
+      <c r="B24" s="18">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25">
-        <v>40</v>
+        <v>152</v>
+      </c>
+      <c r="B25" s="18">
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26">
-        <v>39.5</v>
+        <v>192</v>
+      </c>
+      <c r="B26" s="18">
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B27">
-        <v>39.5</v>
+        <v>159</v>
+      </c>
+      <c r="B27" s="18">
+        <v>47.5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28">
-        <v>39.5</v>
+        <v>84</v>
+      </c>
+      <c r="B28" s="18">
+        <v>47.5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29">
-        <v>39.5</v>
+        <v>147</v>
+      </c>
+      <c r="B29" s="18">
+        <v>47.5</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30">
-        <v>39.5</v>
+        <v>179</v>
+      </c>
+      <c r="B30" s="18">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B31">
-        <v>39.5</v>
+        <v>178</v>
+      </c>
+      <c r="B31" s="18">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32">
-        <v>39</v>
+        <v>156</v>
+      </c>
+      <c r="B32" s="18">
+        <v>46.5</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33">
-        <v>39</v>
+        <v>166</v>
+      </c>
+      <c r="B33" s="18">
+        <v>46.5</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B34">
-        <v>39</v>
+        <v>170</v>
+      </c>
+      <c r="B34" s="18">
+        <v>46.5</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="B35">
-        <v>38.5</v>
+        <v>168</v>
+      </c>
+      <c r="B35" s="18">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36">
-        <v>38.5</v>
+        <v>153</v>
+      </c>
+      <c r="B36" s="18">
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B37">
-        <v>38.5</v>
+        <v>160</v>
+      </c>
+      <c r="B37" s="18">
+        <v>45.5</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B38">
-        <v>38.5</v>
+        <v>202</v>
+      </c>
+      <c r="B38" s="18">
+        <v>45.5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B39">
-        <v>37.5</v>
+        <v>203</v>
+      </c>
+      <c r="B39" s="18">
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B40">
-        <v>37.5</v>
+      <c r="B40" s="18">
+        <v>44.5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41">
-        <v>37.5</v>
+      <c r="B41" s="18">
+        <v>44.5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42">
-        <v>36.5</v>
+        <v>172</v>
+      </c>
+      <c r="B42" s="18">
+        <v>44.5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B43">
-        <v>36.5</v>
+        <v>193</v>
+      </c>
+      <c r="B43" s="18">
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44">
-        <v>36</v>
+        <v>175</v>
+      </c>
+      <c r="B44" s="18">
+        <v>42.5</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B45">
-        <v>34.5</v>
+        <v>182</v>
+      </c>
+      <c r="B45" s="18">
+        <v>42.5</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B46">
-        <v>34.5</v>
+        <v>130</v>
+      </c>
+      <c r="B46" s="18">
+        <v>42.5</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47">
-        <v>34.5</v>
+        <v>198</v>
+      </c>
+      <c r="B47" s="18">
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48">
-        <v>32.5</v>
+        <v>213</v>
+      </c>
+      <c r="B48" s="18">
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B49">
-        <v>28.5</v>
+      <c r="B49" s="18">
+        <v>38.5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B50">
-        <v>1906</v>
+      <c r="B50" s="18">
+        <v>2298</v>
       </c>
     </row>
   </sheetData>
@@ -20708,6 +20741,7 @@
       <c r="A38" t="s">
         <v>128</v>
       </c>
+      <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8993165-A050-465E-AB04-EA8CBA683006}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB7B02F-D8FD-42C3-A0F7-CEB028CB1E06}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3804" uniqueCount="249">
   <si>
     <t>Participants</t>
   </si>
@@ -846,7 +846,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,12 +893,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -942,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -967,9 +961,6 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -988,7 +979,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marc Llopis" refreshedDate="46196.49204571759" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marc Llopis" refreshedDate="46191.502336689817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CF49" sheet="Porra"/>
   </cacheSource>
@@ -1265,13 +1256,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Punts Grups 1r" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16" maxValue="22"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="13" maxValue="19"/>
     </cacheField>
     <cacheField name="Punts Grups 2n" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="11" maxValue="18"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8" maxValue="16"/>
     </cacheField>
     <cacheField name="Punts Grups 3r" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.5" maxValue="15.5"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.5" maxValue="12.5"/>
     </cacheField>
     <cacheField name="Punts Vuitens" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
@@ -1292,13 +1283,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Punts Pichichi" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Resultat Final2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Total Punts" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="38.5" maxValue="56"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="28.5" maxValue="45.5"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1384,18 +1375,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="21"/>
-    <n v="13"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="47.5"/>
+    <n v="18"/>
+    <n v="12"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="39"/>
   </r>
   <r>
     <x v="1"/>
@@ -1470,18 +1461,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="21"/>
-    <n v="16"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="52"/>
+    <n v="18"/>
+    <n v="15"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="45.5"/>
   </r>
   <r>
     <x v="2"/>
@@ -1556,18 +1547,18 @@
     <m/>
     <s v="Rodri"/>
     <s v="Nico Williams"/>
-    <n v="21"/>
-    <n v="14"/>
-    <n v="7.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="18"/>
+    <n v="13"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="40"/>
   </r>
   <r>
     <x v="3"/>
@@ -1642,18 +1633,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="22"/>
-    <n v="18"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="56"/>
+    <n v="17"/>
+    <n v="14"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="45.5"/>
   </r>
   <r>
     <x v="4"/>
@@ -1728,18 +1719,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="15"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="49.5"/>
+    <n v="16"/>
+    <n v="13"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="41.5"/>
   </r>
   <r>
     <x v="5"/>
@@ -1814,18 +1805,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="21"/>
-    <n v="15"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="51"/>
+    <n v="19"/>
+    <n v="13"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="44.5"/>
   </r>
   <r>
     <x v="6"/>
@@ -1900,18 +1891,18 @@
     <m/>
     <s v="Julián Álvarez"/>
     <s v="Julián Álvarez"/>
-    <n v="20"/>
-    <n v="12"/>
-    <n v="6.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="38.5"/>
+    <n v="14"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="28.5"/>
   </r>
   <r>
     <x v="7"/>
@@ -1986,18 +1977,18 @@
     <s v="1-3"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="14"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="47.5"/>
+    <n v="15"/>
+    <n v="13"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="8"/>
@@ -2072,18 +2063,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Kylian Mbappé"/>
-    <n v="20"/>
-    <n v="16"/>
-    <n v="14"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="54"/>
+    <n v="15"/>
+    <n v="13"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="40.5"/>
   </r>
   <r>
     <x v="9"/>
@@ -2158,18 +2149,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="17"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="48"/>
+    <n v="16"/>
+    <n v="15"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="42"/>
   </r>
   <r>
     <x v="10"/>
@@ -2244,18 +2235,18 @@
     <m/>
     <s v="Julián Álvarez"/>
     <s v="Kylian Mbappé"/>
-    <n v="16"/>
-    <n v="15"/>
+    <n v="13"/>
     <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="46"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="36.5"/>
   </r>
   <r>
     <x v="11"/>
@@ -2330,18 +2321,18 @@
     <m/>
     <s v="Harry Kane"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="15"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="48.5"/>
+    <n v="13"/>
+    <n v="12"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="12"/>
@@ -2416,18 +2407,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Lamine Yamal"/>
-    <n v="21"/>
-    <n v="13"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="46.5"/>
+    <n v="18"/>
+    <n v="12"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="13"/>
@@ -2502,18 +2493,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Julián Álvarez"/>
-    <n v="20"/>
     <n v="17"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="49.5"/>
+    <n v="15"/>
+    <n v="7.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="14"/>
@@ -2588,18 +2579,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Julián Álvarez"/>
-    <n v="22"/>
-    <n v="15"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="47.5"/>
+    <n v="19"/>
+    <n v="13"/>
+    <n v="7.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="15"/>
@@ -2674,18 +2665,18 @@
     <m/>
     <s v="Raphinha"/>
     <s v="Erling Haaland"/>
-    <n v="20"/>
-    <n v="11"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="45.5"/>
+    <n v="16"/>
+    <n v="8"/>
+    <n v="12.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="38.5"/>
   </r>
   <r>
     <x v="16"/>
@@ -2760,18 +2751,18 @@
     <s v="2-0"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="13"/>
-    <n v="8.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="44.5"/>
+    <n v="16"/>
+    <n v="12"/>
+    <n v="7.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="37.5"/>
   </r>
   <r>
     <x v="17"/>
@@ -2846,18 +2837,18 @@
     <m/>
     <s v="Vinícius Júnior"/>
     <s v="Vinícius Júnior"/>
-    <n v="20"/>
+    <n v="17"/>
     <n v="13"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="46.5"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="18"/>
@@ -2932,18 +2923,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="12"/>
+    <n v="16"/>
     <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="46"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="39"/>
   </r>
   <r>
     <x v="19"/>
@@ -3018,18 +3009,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="50"/>
+    <n v="16"/>
+    <n v="11"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="20"/>
@@ -3104,18 +3095,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
     <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="46.5"/>
+    <n v="11"/>
+    <n v="8.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="34.5"/>
   </r>
   <r>
     <x v="21"/>
@@ -3190,9 +3181,9 @@
     <m/>
     <s v="Erling Haaland"/>
     <s v="Harry Kane"/>
-    <n v="19"/>
     <n v="13"/>
-    <n v="10.5"/>
+    <n v="11"/>
+    <n v="8.5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -3201,7 +3192,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="44.5"/>
+    <n v="34.5"/>
   </r>
   <r>
     <x v="22"/>
@@ -3276,18 +3267,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Kylian Mbappé"/>
-    <n v="21"/>
-    <n v="17"/>
-    <n v="14"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="56"/>
+    <n v="18"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="23"/>
@@ -3362,18 +3353,18 @@
     <m/>
     <s v="Kylian Mbappé"/>
     <s v="Rodri"/>
-    <n v="19"/>
     <n v="13"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="11"/>
+    <n v="8.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="32.5"/>
   </r>
   <r>
     <x v="24"/>
@@ -3448,18 +3439,18 @@
     <s v="2026-01-02"/>
     <s v="Kylian Mbappé"/>
     <s v="Kylian Mbappé"/>
-    <n v="20"/>
-    <n v="15"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="48"/>
+    <n v="16"/>
+    <n v="13"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="25"/>
@@ -3534,18 +3525,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="18"/>
     <n v="15"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="47"/>
+    <n v="11"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="36.5"/>
   </r>
   <r>
     <x v="26"/>
@@ -3620,18 +3611,18 @@
     <m/>
     <s v="Doué"/>
     <s v="Kylian Mbappé"/>
-    <n v="18"/>
-    <n v="14"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="47"/>
+    <n v="16"/>
+    <n v="13"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="41.5"/>
   </r>
   <r>
     <x v="27"/>
@@ -3706,18 +3697,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="22"/>
-    <n v="11"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="48"/>
+    <n v="17"/>
+    <n v="10"/>
+    <n v="9.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="38.5"/>
   </r>
   <r>
     <x v="28"/>
@@ -3792,18 +3783,18 @@
     <m/>
     <s v="Pedri"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="18"/>
-    <n v="13"/>
-    <n v="9.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="42.5"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="36"/>
   </r>
   <r>
     <x v="29"/>
@@ -3878,18 +3869,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="20"/>
-    <n v="14"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="50.5"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="9.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="38.5"/>
   </r>
   <r>
     <x v="30"/>
@@ -3964,18 +3955,18 @@
     <s v="2026-02-01"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="22"/>
-    <n v="16"/>
-    <n v="9.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="51.5"/>
+    <n v="17"/>
+    <n v="14"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="42"/>
   </r>
   <r>
     <x v="31"/>
@@ -4050,18 +4041,18 @@
     <s v="2026-01-03"/>
     <s v="Lamine Yamal"/>
     <s v="Mikel Oyarzabal"/>
-    <n v="19"/>
-    <n v="15"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="48"/>
+    <n v="16"/>
+    <n v="11"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="37.5"/>
   </r>
   <r>
     <x v="32"/>
@@ -4136,18 +4127,18 @@
     <s v="2026-02-03"/>
     <s v="Harry Kane"/>
     <s v="Kylian Mbappé"/>
-    <n v="21"/>
-    <n v="16"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="50"/>
+    <n v="18"/>
+    <n v="14"/>
+    <n v="8.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="33"/>
@@ -4222,9 +4213,9 @@
     <m/>
     <s v="Vinícius Júnior"/>
     <s v="Harry Kane"/>
-    <n v="18"/>
-    <n v="14"/>
-    <n v="15.5"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="12"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4233,7 +4224,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="49.5"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="34"/>
@@ -4308,9 +4299,9 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Harry Kane"/>
-    <n v="18"/>
-    <n v="13"/>
-    <n v="15"/>
+    <n v="16"/>
+    <n v="12"/>
+    <n v="12"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4319,7 +4310,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="48"/>
+    <n v="42"/>
   </r>
   <r>
     <x v="35"/>
@@ -4394,18 +4385,18 @@
     <m/>
     <s v="Vitinha"/>
     <s v="Endrick"/>
-    <n v="18"/>
+    <n v="17"/>
     <n v="15"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="43"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="42.5"/>
   </r>
   <r>
     <x v="36"/>
@@ -4480,18 +4471,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="19"/>
-    <n v="14"/>
-    <n v="12.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="49.5"/>
+    <n v="16"/>
+    <n v="12"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="40.5"/>
   </r>
   <r>
     <x v="37"/>
@@ -4566,18 +4557,18 @@
     <s v="2026-02-02"/>
     <s v="Pedri"/>
     <s v="Sørloth"/>
-    <n v="18"/>
-    <n v="13"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="42"/>
+    <n v="17"/>
+    <n v="12"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="38"/>
@@ -4652,18 +4643,18 @@
     <s v="2026-01-02"/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="17"/>
-    <n v="13"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="45.5"/>
+    <n v="15"/>
+    <n v="12"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="41"/>
   </r>
   <r>
     <x v="39"/>
@@ -4738,18 +4729,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Julián Álvarez"/>
-    <n v="21"/>
-    <n v="16"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="45"/>
+    <n v="18"/>
+    <n v="12"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="39"/>
   </r>
   <r>
     <x v="40"/>
@@ -4824,18 +4815,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="22"/>
     <n v="17"/>
-    <n v="11.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="54.5"/>
+    <n v="15"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="45"/>
   </r>
   <r>
     <x v="41"/>
@@ -4910,9 +4901,9 @@
     <s v="2026-01-03"/>
     <s v="Lamine Yamal"/>
     <s v="Harry Kane"/>
-    <n v="19"/>
-    <n v="14"/>
-    <n v="13.5"/>
+    <n v="16"/>
+    <n v="13"/>
+    <n v="12"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4921,7 +4912,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="48.5"/>
+    <n v="43"/>
   </r>
   <r>
     <x v="42"/>
@@ -4996,18 +4987,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="20"/>
-    <n v="15"/>
-    <n v="14.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="53.5"/>
+    <n v="17"/>
+    <n v="14"/>
+    <n v="11.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="44.5"/>
   </r>
   <r>
     <x v="43"/>
@@ -5082,9 +5073,9 @@
     <m/>
     <s v="Kylian Mbappé"/>
     <s v="Harry Kane"/>
-    <n v="19"/>
-    <n v="14"/>
-    <n v="14"/>
+    <n v="17"/>
+    <n v="12"/>
+    <n v="7.5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5093,7 +5084,7 @@
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="49"/>
+    <n v="38.5"/>
   </r>
   <r>
     <x v="44"/>
@@ -5168,18 +5159,18 @@
     <s v="2026-04-03"/>
     <s v="Lamine Yamal"/>
     <s v="Ferran Torres"/>
-    <n v="21"/>
-    <n v="16"/>
-    <n v="15"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="52"/>
+    <n v="18"/>
+    <n v="14"/>
+    <n v="8.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="40.5"/>
   </r>
   <r>
     <x v="45"/>
@@ -5254,18 +5245,18 @@
     <m/>
     <s v="Lionel Messi"/>
     <s v="Lamine Yamal"/>
-    <n v="18"/>
-    <n v="11"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="41"/>
+    <n v="14"/>
+    <n v="10"/>
+    <n v="10.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="34.5"/>
   </r>
   <r>
     <x v="46"/>
@@ -5340,18 +5331,18 @@
     <m/>
     <s v="Lamine Yamal"/>
     <s v="Kylian Mbappé"/>
-    <n v="21"/>
-    <n v="18"/>
-    <n v="10.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="53.5"/>
+    <n v="16"/>
+    <n v="15"/>
+    <n v="6.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="39.5"/>
   </r>
   <r>
     <x v="47"/>
@@ -5426,24 +5417,24 @@
     <s v="3-1"/>
     <s v="Kylian Mbappé"/>
     <s v="Lamine Yamal"/>
-    <n v="21"/>
-    <n v="16"/>
-    <n v="7.5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="44.5"/>
+    <n v="15"/>
+    <n v="13"/>
+    <n v="9.5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="37.5"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -5603,7 +5594,7 @@
   </rowFields>
   <rowItems count="49">
     <i>
-      <x v="35"/>
+      <x v="47"/>
     </i>
     <i>
       <x v="26"/>
@@ -5612,64 +5603,25 @@
       <x v="7"/>
     </i>
     <i>
-      <x v="10"/>
+      <x v="39"/>
     </i>
     <i>
       <x v="24"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="31"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="35"/>
     </i>
     <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="14"/>
+      <x v="19"/>
     </i>
     <i>
       <x v="30"/>
     </i>
     <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="40"/>
+      <x v="16"/>
     </i>
     <i>
       <x v="33"/>
@@ -5678,43 +5630,82 @@
       <x v="27"/>
     </i>
     <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
       <x v="49"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="42"/>
     </i>
     <i>
       <x v="11"/>
     </i>
     <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
       <x v="9"/>
     </i>
     <i>
-      <x v="20"/>
+      <x v="28"/>
     </i>
     <i>
       <x v="32"/>
     </i>
     <i>
-      <x v="21"/>
+      <x v="40"/>
     </i>
     <i>
-      <x v="42"/>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="38"/>
     </i>
     <i>
       <x v="13"/>
@@ -5723,25 +5714,25 @@
       <x v="50"/>
     </i>
     <i>
-      <x v="51"/>
+      <x v="20"/>
     </i>
     <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="52"/>
+      <x v="22"/>
     </i>
     <i>
       <x v="37"/>
     </i>
     <i>
-      <x v="25"/>
+      <x v="18"/>
     </i>
     <i>
-      <x v="17"/>
+      <x v="15"/>
     </i>
     <i>
-      <x v="18"/>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
     </i>
     <i>
       <x v="3"/>
@@ -6120,9 +6111,8 @@
       <c r="C2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="14" t="str">
-        <f>+C2</f>
-        <v>Mèxic</v>
+      <c r="E2" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>229</v>
@@ -6149,7 +6139,7 @@
         <v>158</v>
       </c>
       <c r="O2" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -6162,9 +6152,8 @@
       <c r="C3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="14" t="str">
-        <f>+C3</f>
-        <v>Corea del Sud</v>
+      <c r="E3" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>229</v>
@@ -6182,7 +6171,7 @@
         <v>162</v>
       </c>
       <c r="O3" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -6192,12 +6181,11 @@
       <c r="B4" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="14" t="str">
-        <f>+C5</f>
-        <v>Canadà</v>
+      <c r="E4" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>229</v>
@@ -6209,10 +6197,10 @@
         <v>229</v>
       </c>
       <c r="N4" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="O4" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -6225,9 +6213,8 @@
       <c r="C5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="14" t="str">
-        <f>+C6</f>
-        <v>Suïssa</v>
+      <c r="E5" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>229</v>
@@ -6239,7 +6226,7 @@
         <v>229</v>
       </c>
       <c r="N5" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="O5" s="3">
         <v>2</v>
@@ -6255,9 +6242,8 @@
       <c r="C6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="14" t="str">
-        <f>+C8</f>
-        <v>Brasil</v>
+      <c r="E6" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>229</v>
@@ -6279,12 +6265,11 @@
       <c r="B7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E7" s="14" t="str">
-        <f>+C9</f>
-        <v>Marroc</v>
+      <c r="E7" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>229</v>
@@ -6293,10 +6278,10 @@
         <v>229</v>
       </c>
       <c r="N7" t="s">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="O7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -6309,9 +6294,8 @@
       <c r="C8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="14" t="str">
-        <f>+C11</f>
-        <v>Estats Units</v>
+      <c r="E8" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>229</v>
@@ -6320,7 +6304,7 @@
         <v>229</v>
       </c>
       <c r="N8" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -6336,9 +6320,8 @@
       <c r="C9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="14" t="str">
-        <f>+C12</f>
-        <v>Austràlia</v>
+      <c r="E9" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>229</v>
@@ -6347,7 +6330,7 @@
         <v>229</v>
       </c>
       <c r="N9" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -6360,18 +6343,17 @@
       <c r="B10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="14" t="str">
-        <f>+C14</f>
-        <v>Alemanya</v>
+      <c r="E10" s="14" t="s">
+        <v>143</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N10" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -6387,18 +6369,17 @@
       <c r="C11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="14" t="str">
-        <f>+C15</f>
-        <v>Costa d'Ivori</v>
+      <c r="E11" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>229</v>
       </c>
       <c r="N11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -6411,9 +6392,8 @@
       <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="14" t="str">
-        <f>+C17</f>
-        <v>Països Baixos</v>
+      <c r="E12" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>229</v>
@@ -6432,12 +6412,11 @@
       <c r="B13" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="14" t="str">
-        <f>+C18</f>
-        <v>Japó</v>
+      <c r="E13" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>229</v>
@@ -6459,9 +6438,8 @@
       <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="14" t="str">
-        <f>+C20</f>
-        <v>Egipte</v>
+      <c r="E14" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>229</v>
@@ -6483,9 +6461,8 @@
       <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="14" t="str">
-        <f>+C21</f>
-        <v>Iran</v>
+      <c r="E15" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>229</v>
@@ -6498,12 +6475,11 @@
       <c r="B16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="14" t="str">
-        <f>+C23</f>
-        <v>Espanya</v>
+      <c r="E16" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>229</v>
@@ -6519,9 +6495,8 @@
       <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="14" t="str">
-        <f>+C24</f>
-        <v>Uruguai</v>
+      <c r="E17" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>229</v>
@@ -6537,9 +6512,8 @@
       <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="14" t="str">
-        <f>+C26</f>
-        <v>França</v>
+      <c r="E18" s="14" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6549,12 +6523,11 @@
       <c r="B19" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="14" t="str">
-        <f>+C27</f>
-        <v>Noruega</v>
+      <c r="E19" s="14" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6567,9 +6540,8 @@
       <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="14" t="str">
-        <f>+C29</f>
-        <v>Argentina</v>
+      <c r="E20" s="14" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,9 +6554,8 @@
       <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="14" t="str">
-        <f>+C30</f>
-        <v>Àustria</v>
+      <c r="E21" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,12 +6565,11 @@
       <c r="B22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="14" t="str">
-        <f>+C32</f>
-        <v>Colòmbia</v>
+      <c r="E22" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6612,9 +6582,8 @@
       <c r="C23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="14" t="str">
-        <f>+C33</f>
-        <v>RD Congo</v>
+      <c r="E23" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6627,9 +6596,8 @@
       <c r="C24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="14" t="str">
-        <f>+C35</f>
-        <v>Anglaterra</v>
+      <c r="E24" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6639,12 +6607,11 @@
       <c r="B25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="14" t="str">
-        <f>+C36</f>
-        <v>Ghana</v>
+      <c r="E25" s="14" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6655,10 +6622,10 @@
         <v>228</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -6670,10 +6637,10 @@
         <v>230</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6683,11 +6650,11 @@
       <c r="B28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="3" t="s">
         <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -6701,7 +6668,7 @@
         <v>95</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6715,7 +6682,7 @@
         <v>107</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -6725,11 +6692,11 @@
       <c r="B31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>119</v>
+      <c r="C31" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,7 +6724,7 @@
         <v>128</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6767,7 +6734,7 @@
       <c r="B34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="3" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6790,7 +6757,7 @@
         <v>230</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6800,8 +6767,8 @@
       <c r="B37" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>145</v>
+      <c r="C37" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -7394,15 +7361,15 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7438,7 +7405,7 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>47.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.25">
@@ -7657,7 +7624,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
@@ -7665,7 +7632,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7693,7 +7660,7 @@
       </c>
       <c r="CD3">
         <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE3">
         <f>IF(BR3='Resultats Reals'!$L$2,5,0)</f>
@@ -7701,7 +7668,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.25">
@@ -7920,15 +7887,15 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7964,7 +7931,7 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.25">
@@ -8183,15 +8150,15 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8219,7 +8186,7 @@
       </c>
       <c r="CD5">
         <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE5">
         <f>IF(BR5='Resultats Reals'!$L$2,5,0)</f>
@@ -8227,7 +8194,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.25">
@@ -8446,7 +8413,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
@@ -8454,7 +8421,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8482,7 +8449,7 @@
       </c>
       <c r="CD6">
         <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE6">
         <f>IF(BR6='Resultats Reals'!$L$2,5,0)</f>
@@ -8490,7 +8457,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8709,7 +8676,7 @@
       </c>
       <c r="BU7">
         <f>IF(C7='Resultats Reals'!$C$2,2,IF(OR(C7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C7)&gt;0),1,0))+IF(D7='Resultats Reals'!$C$5,2,IF(OR(D7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D7)&gt;0),1,0))+IF(E7='Resultats Reals'!$C$8,2,IF(OR(E7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E7)&gt;0),1,0))+IF(F7='Resultats Reals'!$C$11,2,IF(OR(F7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F7)&gt;0),1,0))+IF(G7='Resultats Reals'!$C$14,2,IF(OR(G7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G7)&gt;0),1,0))+IF(H7='Resultats Reals'!$C$17,2,IF(OR(H7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H7)&gt;0),1,0))+IF(I7='Resultats Reals'!$C$20,2,IF(OR(I7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I7)&gt;0),1,0))+IF(J7='Resultats Reals'!$C$23,2,IF(OR(J7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J7)&gt;0),1,0))+IF(K7='Resultats Reals'!$C$26,2,IF(OR(K7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K7)&gt;0),1,0))+IF(L7='Resultats Reals'!$C$29,2,IF(OR(L7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L7)&gt;0),1,0))+IF(M7='Resultats Reals'!$C$32,2,IF(OR(M7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M7)&gt;0),1,0))+IF(N7='Resultats Reals'!$C$35,2,IF(OR(N7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N7)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z7)&gt;0),1,0))</f>
@@ -8717,7 +8684,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8745,7 +8712,7 @@
       </c>
       <c r="CD7">
         <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE7">
         <f>IF(BR7='Resultats Reals'!$L$2,5,0)</f>
@@ -8753,7 +8720,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.25">
@@ -8976,7 +8943,7 @@
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
@@ -9016,7 +8983,7 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.25">
@@ -9238,15 +9205,15 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N9)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z9)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9274,7 +9241,7 @@
       </c>
       <c r="CD9">
         <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE9">
         <f>IF(BR9='Resultats Reals'!$L$2,5,0)</f>
@@ -9282,7 +9249,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.25">
@@ -9501,15 +9468,15 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
@@ -9537,7 +9504,7 @@
       </c>
       <c r="CD10">
         <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE10">
         <f>IF(BR10='Resultats Reals'!$L$2,5,0)</f>
@@ -9545,7 +9512,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
@@ -9764,7 +9731,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
@@ -9800,7 +9767,7 @@
       </c>
       <c r="CD11">
         <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE11">
         <f>IF(BR11='Resultats Reals'!$L$2,5,0)</f>
@@ -9808,7 +9775,7 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
@@ -10031,11 +9998,11 @@
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
@@ -10063,7 +10030,7 @@
       </c>
       <c r="CD12">
         <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE12">
         <f>IF(BR12='Resultats Reals'!$L$2,5,0)</f>
@@ -10071,7 +10038,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.25">
@@ -10290,15 +10257,15 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10326,7 +10293,7 @@
       </c>
       <c r="CD13">
         <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE13">
         <f>IF(BR13='Resultats Reals'!$L$2,5,0)</f>
@@ -10334,7 +10301,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>48.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.25">
@@ -10553,15 +10520,15 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
@@ -10597,7 +10564,7 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.25">
@@ -10816,7 +10783,7 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
@@ -10824,7 +10791,7 @@
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
@@ -10860,7 +10827,7 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.25">
@@ -11079,7 +11046,7 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
@@ -11087,7 +11054,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11123,7 +11090,7 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.25">
@@ -11342,15 +11309,15 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N17)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX17">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
@@ -11378,7 +11345,7 @@
       </c>
       <c r="CD17">
         <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE17">
         <f>IF(BR17='Resultats Reals'!$L$2,5,0)</f>
@@ -11386,7 +11353,7 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.25">
@@ -11608,11 +11575,11 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
@@ -11644,7 +11611,7 @@
       </c>
       <c r="CD18">
         <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE18">
         <f>IF(BR18='Resultats Reals'!$L$2,5,0)</f>
@@ -11652,7 +11619,7 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
@@ -11871,15 +11838,15 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -12134,15 +12101,15 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12170,7 +12137,7 @@
       </c>
       <c r="CD20">
         <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE20">
         <f>IF(BR20='Resultats Reals'!$L$2,5,0)</f>
@@ -12178,7 +12145,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
@@ -12397,7 +12364,7 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
@@ -12405,7 +12372,7 @@
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
@@ -12433,7 +12400,7 @@
       </c>
       <c r="CD21">
         <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE21">
         <f>IF(BR21='Resultats Reals'!$L$2,5,0)</f>
@@ -12441,7 +12408,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.25">
@@ -12664,11 +12631,11 @@
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX22">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB22)&gt;0,1,0)</f>
@@ -12696,7 +12663,7 @@
       </c>
       <c r="CD22">
         <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE22">
         <f>IF(BR22='Resultats Reals'!$L$2,5,0)</f>
@@ -12704,7 +12671,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.25">
@@ -12927,11 +12894,11 @@
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX23">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB23)&gt;0,1,0)</f>
@@ -12967,7 +12934,7 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.25">
@@ -13186,7 +13153,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
@@ -13194,7 +13161,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13222,7 +13189,7 @@
       </c>
       <c r="CD24">
         <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE24">
         <f>IF(BR24='Resultats Reals'!$L$2,5,0)</f>
@@ -13230,7 +13197,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
@@ -13453,11 +13420,11 @@
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX25">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB25)&gt;0,1,0)</f>
@@ -13493,7 +13460,7 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="26" spans="1:84" x14ac:dyDescent="0.25">
@@ -13715,7 +13682,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
@@ -13723,7 +13690,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13751,7 +13718,7 @@
       </c>
       <c r="CD26">
         <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE26">
         <f>IF(BR26='Resultats Reals'!$L$2,5,0)</f>
@@ -13759,7 +13726,7 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
@@ -13978,15 +13945,15 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
@@ -14022,7 +13989,7 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.25">
@@ -14241,7 +14208,7 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N28)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z28)&gt;0),1,0))</f>
@@ -14249,7 +14216,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14277,7 +14244,7 @@
       </c>
       <c r="CD28">
         <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE28">
         <f>IF(BR28='Resultats Reals'!$L$2,5,0)</f>
@@ -14285,7 +14252,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.25">
@@ -14507,15 +14474,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14543,7 +14510,7 @@
       </c>
       <c r="CD29">
         <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE29">
         <f>IF(BR29='Resultats Reals'!$L$2,5,0)</f>
@@ -14551,7 +14518,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.25">
@@ -14770,15 +14737,15 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14814,7 +14781,7 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.25">
@@ -15033,7 +15000,7 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
@@ -15041,7 +15008,7 @@
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX31">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
@@ -15069,7 +15036,7 @@
       </c>
       <c r="CD31">
         <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE31">
         <f>IF(BR31='Resultats Reals'!$L$2,5,0)</f>
@@ -15077,7 +15044,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
@@ -15299,15 +15266,15 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15335,7 +15302,7 @@
       </c>
       <c r="CD32">
         <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE32">
         <f>IF(BR32='Resultats Reals'!$L$2,5,0)</f>
@@ -15343,7 +15310,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>51.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
@@ -15565,7 +15532,7 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
@@ -15573,7 +15540,7 @@
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
@@ -15609,7 +15576,7 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.25">
@@ -15831,15 +15798,15 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15867,7 +15834,7 @@
       </c>
       <c r="CD34">
         <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE34">
         <f>IF(BR34='Resultats Reals'!$L$2,5,0)</f>
@@ -15875,7 +15842,7 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
@@ -16094,15 +16061,15 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
@@ -16357,15 +16324,15 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N36)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z36)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16401,7 +16368,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.25">
@@ -16620,15 +16587,15 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16664,7 +16631,7 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.25">
@@ -16886,7 +16853,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
@@ -16894,7 +16861,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16922,7 +16889,7 @@
       </c>
       <c r="CD38">
         <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE38">
         <f>IF(BR38='Resultats Reals'!$L$2,5,0)</f>
@@ -16930,7 +16897,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
@@ -17152,15 +17119,15 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N39)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
@@ -17196,7 +17163,7 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.25">
@@ -17422,11 +17389,11 @@
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z40)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17454,7 +17421,7 @@
       </c>
       <c r="CD40">
         <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE40">
         <f>IF(BR40='Resultats Reals'!$L$2,5,0)</f>
@@ -17462,7 +17429,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
@@ -17681,7 +17648,7 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N41)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
@@ -17689,7 +17656,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
@@ -17725,7 +17692,7 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.25">
@@ -17944,15 +17911,15 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N42)&gt;0),1,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z42)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17980,7 +17947,7 @@
       </c>
       <c r="CD42">
         <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE42">
         <f>IF(BR42='Resultats Reals'!$L$2,5,0)</f>
@@ -17988,7 +17955,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>54.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.25">
@@ -18210,15 +18177,15 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N43)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z43)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
@@ -18473,15 +18440,15 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N44)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z44)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18509,7 +18476,7 @@
       </c>
       <c r="CD44">
         <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE44">
         <f>IF(BR44='Resultats Reals'!$L$2,5,0)</f>
@@ -18517,7 +18484,7 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>53.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.25">
@@ -18736,7 +18703,7 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N45)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z45)&gt;0),1,0))</f>
@@ -18744,7 +18711,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18780,7 +18747,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.25">
@@ -19002,15 +18969,15 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N46)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z46)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -19046,7 +19013,7 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.25">
@@ -19265,15 +19232,15 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N47)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z47)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
@@ -19309,7 +19276,7 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.25">
@@ -19528,15 +19495,15 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N48)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z48)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19564,7 +19531,7 @@
       </c>
       <c r="CD48">
         <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CE48">
         <f>IF(BR48='Resultats Reals'!$L$2,5,0)</f>
@@ -19572,7 +19539,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>53.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.25">
@@ -19794,15 +19761,15 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N49)&gt;0),1,0))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z49)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19838,7 +19805,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -19865,394 +19832,394 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="18">
-        <v>56</v>
+        <v>124</v>
+      </c>
+      <c r="B2">
+        <v>45.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="18">
-        <v>56</v>
+      <c r="B3">
+        <v>45.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="18">
-        <v>54.5</v>
+      <c r="B4">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="18">
-        <v>54</v>
+        <v>138</v>
+      </c>
+      <c r="B5">
+        <v>44.5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="18">
-        <v>53.5</v>
+      <c r="B6">
+        <v>44.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="18">
-        <v>53.5</v>
+        <v>206</v>
+      </c>
+      <c r="B7">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="18">
-        <v>52</v>
+        <v>174</v>
+      </c>
+      <c r="B8">
+        <v>42.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="18">
-        <v>52</v>
+        <v>193</v>
+      </c>
+      <c r="B9">
+        <v>42.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="18">
-        <v>51.5</v>
+        <v>189</v>
+      </c>
+      <c r="B10">
+        <v>42.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="18">
-        <v>51</v>
+        <v>185</v>
+      </c>
+      <c r="B11">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="18">
-        <v>50.5</v>
+        <v>152</v>
+      </c>
+      <c r="B12">
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="18">
-        <v>50</v>
+        <v>192</v>
+      </c>
+      <c r="B13">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="18">
-        <v>50</v>
+        <v>137</v>
+      </c>
+      <c r="B14">
+        <v>41.5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="18">
-        <v>49.5</v>
+        <v>179</v>
+      </c>
+      <c r="B15">
+        <v>41.5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="18">
-        <v>49.5</v>
+        <v>147</v>
+      </c>
+      <c r="B16">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B17" s="18">
-        <v>49.5</v>
+        <v>202</v>
+      </c>
+      <c r="B17">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="18">
-        <v>49.5</v>
+        <v>166</v>
+      </c>
+      <c r="B18">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="B19" s="18">
-        <v>49</v>
+        <v>191</v>
+      </c>
+      <c r="B19">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="18">
-        <v>48.5</v>
+        <v>156</v>
+      </c>
+      <c r="B20">
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B21" s="18">
-        <v>48.5</v>
+        <v>176</v>
+      </c>
+      <c r="B21">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B22" s="18">
-        <v>48</v>
+        <v>210</v>
+      </c>
+      <c r="B22">
+        <v>40.5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B23" s="18">
-        <v>48</v>
+        <v>196</v>
+      </c>
+      <c r="B23">
+        <v>40.5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B24" s="18">
-        <v>48</v>
+        <v>150</v>
+      </c>
+      <c r="B24">
+        <v>40.5</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="18">
-        <v>48</v>
+        <v>130</v>
+      </c>
+      <c r="B25">
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B26" s="18">
-        <v>48</v>
+        <v>159</v>
+      </c>
+      <c r="B26">
+        <v>39.5</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B27" s="18">
-        <v>47.5</v>
+        <v>154</v>
+      </c>
+      <c r="B27">
+        <v>39.5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="18">
-        <v>47.5</v>
+        <v>157</v>
+      </c>
+      <c r="B28">
+        <v>39.5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="18">
-        <v>47.5</v>
+        <v>169</v>
+      </c>
+      <c r="B29">
+        <v>39.5</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="18">
-        <v>47</v>
+        <v>214</v>
+      </c>
+      <c r="B30">
+        <v>39.5</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="18">
-        <v>47</v>
+        <v>198</v>
+      </c>
+      <c r="B31">
+        <v>39.5</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B32" s="18">
-        <v>46.5</v>
+        <v>203</v>
+      </c>
+      <c r="B32">
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="18">
-        <v>46.5</v>
+        <v>84</v>
+      </c>
+      <c r="B33">
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B34" s="18">
-        <v>46.5</v>
+        <v>168</v>
+      </c>
+      <c r="B34">
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B35" s="18">
-        <v>46</v>
+        <v>209</v>
+      </c>
+      <c r="B35">
+        <v>38.5</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="18">
-        <v>46</v>
+        <v>160</v>
+      </c>
+      <c r="B36">
+        <v>38.5</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B37" s="18">
-        <v>45.5</v>
+        <v>181</v>
+      </c>
+      <c r="B37">
+        <v>38.5</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="18">
-        <v>45.5</v>
+        <v>184</v>
+      </c>
+      <c r="B38">
+        <v>38.5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" s="18">
-        <v>45</v>
+        <v>187</v>
+      </c>
+      <c r="B39">
+        <v>37.5</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B40" s="18">
-        <v>44.5</v>
+      <c r="B40">
+        <v>37.5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="18">
-        <v>44.5</v>
+      <c r="B41">
+        <v>37.5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="18">
-        <v>44.5</v>
+        <v>153</v>
+      </c>
+      <c r="B42">
+        <v>36.5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="18">
-        <v>43</v>
+        <v>178</v>
+      </c>
+      <c r="B43">
+        <v>36.5</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="18">
-        <v>42.5</v>
+        <v>182</v>
+      </c>
+      <c r="B44">
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B45" s="18">
-        <v>42.5</v>
+        <v>213</v>
+      </c>
+      <c r="B45">
+        <v>34.5</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="18">
-        <v>42.5</v>
+        <v>170</v>
+      </c>
+      <c r="B46">
+        <v>34.5</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="18">
-        <v>42</v>
+        <v>172</v>
+      </c>
+      <c r="B47">
+        <v>34.5</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48" s="18">
-        <v>41</v>
+        <v>175</v>
+      </c>
+      <c r="B48">
+        <v>32.5</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="18">
-        <v>38.5</v>
+      <c r="B49">
+        <v>28.5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B50" s="18">
-        <v>2298</v>
+      <c r="B50">
+        <v>1906</v>
       </c>
     </row>
   </sheetData>
@@ -20741,7 +20708,6 @@
       <c r="A38" t="s">
         <v>128</v>
       </c>
-      <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8993165-A050-465E-AB04-EA8CBA683006}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591B57FF-C5CC-F64C-B8C7-B30F9841C52E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,16 @@
     <sheet name="Gràfics" sheetId="3" r:id="rId3"/>
     <sheet name="Països_ok" sheetId="5" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gràfics!$A$1:$B$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultats Reals'!$N$1:$O$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -964,12 +967,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,6 +988,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Fulla2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5443,7 +5459,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6051,25 +6067,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.47265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.953125" customWidth="1"/>
+    <col min="14" max="14" width="20.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7421875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6110,7 +6128,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6152,7 +6170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6185,14 +6203,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>110</v>
       </c>
       <c r="E4" s="14" t="str">
@@ -6215,7 +6233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6245,7 +6263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6272,14 +6290,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>246</v>
       </c>
       <c r="E7" s="14" t="str">
@@ -6299,7 +6317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6326,7 +6344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6353,14 +6371,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>112</v>
       </c>
       <c r="E10" s="14" t="str">
@@ -6377,7 +6395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6401,7 +6419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6425,14 +6443,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="14" t="str">
@@ -6449,7 +6467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6473,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6491,14 +6509,14 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>102</v>
       </c>
       <c r="E16" s="14" t="str">
@@ -6509,7 +6527,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6527,7 +6545,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6542,14 +6560,14 @@
         <v>França</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="14" t="str">
@@ -6557,7 +6575,7 @@
         <v>Noruega</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6572,7 +6590,7 @@
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6587,14 +6605,14 @@
         <v>Àustria</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="17" t="s">
         <v>92</v>
       </c>
       <c r="E22" s="14" t="str">
@@ -6602,7 +6620,7 @@
         <v>Colòmbia</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6614,10 +6632,10 @@
       </c>
       <c r="E23" s="14" t="str">
         <f>+C33</f>
-        <v>RD Congo</v>
+        <v>Portugal</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6632,14 +6650,14 @@
         <v>Anglaterra</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="17" t="s">
         <v>143</v>
       </c>
       <c r="E25" s="14" t="str">
@@ -6647,7 +6665,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6662,7 +6680,7 @@
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6676,21 +6694,21 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6704,7 +6722,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6718,21 +6736,21 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>119</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6746,7 +6764,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6754,24 +6772,24 @@
         <v>230</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>96</v>
+      <c r="C34" s="17" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6782,7 +6800,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6793,15 +6811,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>145</v>
+      <c r="C37" s="17" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -6831,7 +6849,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -6850,81 +6867,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.45703125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7178,7 +7195,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7402,7 +7419,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7438,10 +7455,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>47.5</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7665,7 +7682,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7701,10 +7718,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7928,7 +7945,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7964,10 +7981,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8187,7 +8204,7 @@
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
@@ -8227,10 +8244,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8450,7 +8467,7 @@
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
@@ -8490,10 +8507,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
     </row>
-    <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8713,11 +8730,11 @@
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z7)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8753,10 +8770,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>53.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8972,7 +8989,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N8)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
@@ -8980,7 +8997,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -9016,10 +9033,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9238,15 +9255,15 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N9)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z9)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9282,10 +9299,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9505,11 +9522,11 @@
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
@@ -9545,10 +9562,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>54.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9772,7 +9789,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$